--- a/docs/data/jp/xlsx/3426.xlsx
+++ b/docs/data/jp/xlsx/3426.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,6 +323,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -717,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC148"/>
+  <dimension ref="A1:AC154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4383,10 +4386,12 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="n"/>
+          <t>현재 주가 (2026.10.23)</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>1308</v>
+      </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
       <c r="E47" s="31" t="n"/>
@@ -4421,7 +4426,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
+      <c r="B48" s="29" t="n">
+        <v>4105000</v>
+      </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="31" t="n"/>
       <c r="E48" s="31" t="n"/>
@@ -5620,7 +5627,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.23</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5872,882 +5879,928 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T79" s="17">
+        <f>IF(OR(T78="",S78=""),"",IF(S78&lt;=0,"",IFERROR(T78/S78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>IF(OR(U78="",T78=""),"",IF(T78&lt;=0,"",IFERROR(U78/T78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>Cost Of Sales</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>1830.059</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>2152.201</v>
       </c>
-      <c r="E79" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>1849.126</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>1801.875</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>1781.475</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>2090.998</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>1858.051</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>1832.827</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>1847.847</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>2116.196</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>1845.059</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>1925.207</v>
       </c>
-      <c r="T79" s="22" t="n">
+      <c r="T80" s="22" t="n">
         <v>1770.904</v>
       </c>
-      <c r="U79" s="22" t="n">
+      <c r="U80" s="22" t="n">
         <v>1904.036</v>
       </c>
-      <c r="V79" s="22" t="n">
+      <c r="V80" s="22" t="n">
         <v>1801.875</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>1832.827</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>1925.207</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>609.088</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>692.405</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>611.354</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>616.371</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>635.018</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>766.293</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>657.254</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>675.099</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>645.842</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>749.747</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>663.694</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>713.0599999999999</v>
       </c>
-      <c r="T80" s="12" t="n">
+      <c r="T81" s="12" t="n">
         <v>652.038</v>
       </c>
-      <c r="U80" s="12" t="n">
+      <c r="U81" s="12" t="n">
         <v>628.263</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>616.371</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>675.099</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>713.0599999999999</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>판매비와 관리비 합계</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>534.567</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>539.487</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>552.98</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>568.682</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>543.737</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>543.63</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>542.341</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>588.479</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>557.728</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>559.316</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>557.6319999999999</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>605.8339999999999</v>
-      </c>
-      <c r="T81" s="22" t="n">
-        <v>582.768</v>
-      </c>
-      <c r="U81" s="22" t="n">
-        <v>585.271</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>568.682</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>588.479</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>605.8339999999999</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>74.52</v>
-      </c>
-      <c r="D82" s="12" t="n">
-        <v>152.918</v>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>58.375</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>47.688</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>91.28100000000001</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>222.662</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>114.914</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>86.619</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>88.113</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>190.432</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>106.061</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>107.226</v>
-      </c>
-      <c r="T82" s="12" t="n">
-        <v>69.27</v>
-      </c>
-      <c r="U82" s="12" t="n">
-        <v>42.993</v>
-      </c>
-      <c r="V82" s="12" t="n">
-        <v>47.688</v>
-      </c>
-      <c r="W82" s="12" t="n">
-        <v>86.619</v>
-      </c>
-      <c r="X82" s="12" t="n">
-        <v>107.226</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T82" s="17">
+        <f>IF(OR(T81="",S81=""),"",IF(S81&lt;=0,"",IFERROR(T81/S81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U82" s="17">
+        <f>IF(OR(U81="",T81=""),"",IF(T81&lt;=0,"",IFERROR(U81/T81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>판매비와 관리비 합계</t>
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>5.625</v>
+        <v>534.567</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>5.982</v>
+        <v>539.487</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>5.807</v>
+        <v>552.98</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>-16.3</v>
+        <v>568.682</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>7.28</v>
+        <v>543.737</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>8.779999999999999</v>
+        <v>543.63</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>8.333</v>
+        <v>542.341</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>-16.938</v>
+        <v>588.479</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>11.585</v>
+        <v>557.728</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>11.802</v>
+        <v>559.316</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>12.745</v>
+        <v>557.6319999999999</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>-18.645</v>
+        <v>605.8339999999999</v>
       </c>
       <c r="T83" s="22" t="n">
-        <v>-10.787</v>
+        <v>582.768</v>
       </c>
       <c r="U83" s="22" t="n">
-        <v>-12.394</v>
+        <v>585.271</v>
       </c>
       <c r="V83" s="22" t="n">
-        <v>-16.3</v>
+        <v>568.682</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>-16.938</v>
+        <v>588.479</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>-18.645</v>
+        <v>605.8339999999999</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>배당금수익</t>
-        </is>
-      </c>
-      <c r="E84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="22" t="n">
-        <v>3.297</v>
-      </c>
-      <c r="G84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" s="22" t="n">
-        <v>3.403</v>
-      </c>
-      <c r="I84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="22" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="K84" s="22" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="L84" s="22" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="M84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" s="22" t="n">
-        <v>6.097</v>
-      </c>
-      <c r="T84" s="22" t="n">
-        <v>3.124</v>
-      </c>
-      <c r="U84" s="22" t="n">
-        <v>2.966</v>
-      </c>
-      <c r="V84" s="22" t="n">
-        <v>3.297</v>
-      </c>
-      <c r="W84" s="22" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="X84" s="22" t="n">
-        <v>6.097</v>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>74.52</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>152.918</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>58.375</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>47.688</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>91.28100000000001</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>222.662</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>114.914</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>86.619</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>88.113</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>190.432</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>106.061</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>107.226</v>
+      </c>
+      <c r="T84" s="12" t="n">
+        <v>69.27</v>
+      </c>
+      <c r="U84" s="12" t="n">
+        <v>42.993</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>47.688</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <v>86.619</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>107.226</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>매입할인</t>
-        </is>
-      </c>
-      <c r="C85" s="22" t="n">
-        <v>1.523</v>
-      </c>
-      <c r="D85" s="22" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E85" s="22" t="n">
-        <v>1.575</v>
-      </c>
-      <c r="F85" s="22" t="n">
-        <v>1.251</v>
-      </c>
-      <c r="G85" s="22" t="n">
-        <v>1.335</v>
-      </c>
-      <c r="H85" s="22" t="n">
-        <v>1.642</v>
-      </c>
-      <c r="I85" s="22" t="n">
-        <v>1.699</v>
-      </c>
-      <c r="J85" s="22" t="n">
-        <v>1.529</v>
-      </c>
-      <c r="K85" s="22" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="L85" s="22" t="n">
-        <v>1.942</v>
-      </c>
-      <c r="M85" s="22" t="n">
-        <v>1.963</v>
-      </c>
-      <c r="N85" s="22" t="n">
-        <v>1.962</v>
-      </c>
-      <c r="T85" s="22" t="n">
-        <v>1.337</v>
-      </c>
-      <c r="U85" s="22" t="n">
-        <v>1.363</v>
-      </c>
-      <c r="V85" s="22" t="n">
-        <v>1.251</v>
-      </c>
-      <c r="W85" s="22" t="n">
-        <v>1.529</v>
-      </c>
-      <c r="X85" s="22" t="n">
-        <v>1.962</v>
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C85" s="17">
+        <f>IF(OR(C84="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C84/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(OR(D84="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D84/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>IF(OR(E84="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E84/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>IF(OR(F84="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F84/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G85" s="17">
+        <f>IF(OR(G84="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G84/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="17">
+        <f>IF(OR(H84="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H84/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="17">
+        <f>IF(OR(I84="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I84/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="17">
+        <f>IF(OR(J84="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J84/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="17">
+        <f>IF(OR(K84="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K84/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="17">
+        <f>IF(OR(L84="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L84/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="17">
+        <f>IF(OR(M84="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M84/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="17">
+        <f>IF(OR(N84="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N84/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="T85" s="17">
+        <f>IF(OR(T84="",T78=""),"",IF(T78&lt;=0,"",IFERROR(T84/T78,"")))</f>
+        <v/>
+      </c>
+      <c r="U85" s="17">
+        <f>IF(OR(U84="",U78=""),"",IF(U78&lt;=0,"",IFERROR(U84/U78,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="17">
+        <f>IF(OR(V84="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V84/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="17">
+        <f>IF(OR(W84="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W84/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="17">
+        <f>IF(OR(X84="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X84/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>외환차익</t>
-        </is>
-      </c>
-      <c r="C86" s="22" t="n">
-        <v>1.877</v>
-      </c>
-      <c r="D86" s="22" t="n">
-        <v>-1.877</v>
-      </c>
-      <c r="E86" s="22" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="F86" s="22" t="n">
-        <v>2.996</v>
-      </c>
-      <c r="G86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" s="22" t="n">
-        <v>1.241</v>
-      </c>
-      <c r="L86" s="22" t="n">
-        <v>2.397</v>
-      </c>
-      <c r="M86" s="22" t="n">
-        <v>1.076</v>
-      </c>
-      <c r="N86" s="22" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="T86" s="22" t="n">
-        <v>4.098</v>
-      </c>
-      <c r="U86" s="22" t="n">
-        <v>4.457</v>
-      </c>
-      <c r="V86" s="22" t="n">
-        <v>2.996</v>
-      </c>
-      <c r="W86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X86" s="22" t="n">
-        <v>0.8149999999999999</v>
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G86" s="17">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="17">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M86" s="17">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="17">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T86" s="17">
+        <f>IF(OR(T84="",S84=""),"",IF(S84&lt;=0,"",IFERROR(T84/S84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U86" s="17">
+        <f>IF(OR(U84="",T84=""),"",IF(T84&lt;=0,"",IFERROR(U84/T84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V86" s="17">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W86" s="17">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X86" s="17">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>대손충당금 환입</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="C87" s="22" t="n">
-        <v>0</v>
+        <v>5.625</v>
+      </c>
+      <c r="D87" s="22" t="n">
+        <v>5.982</v>
+      </c>
+      <c r="E87" s="22" t="n">
+        <v>5.807</v>
+      </c>
+      <c r="F87" s="22" t="n">
+        <v>-16.3</v>
       </c>
       <c r="G87" s="22" t="n">
-        <v>3.132</v>
+        <v>7.28</v>
+      </c>
+      <c r="H87" s="22" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="I87" s="22" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="J87" s="22" t="n">
+        <v>-16.938</v>
       </c>
       <c r="K87" s="22" t="n">
-        <v>0</v>
+        <v>11.585</v>
+      </c>
+      <c r="L87" s="22" t="n">
+        <v>11.802</v>
+      </c>
+      <c r="M87" s="22" t="n">
+        <v>12.745</v>
+      </c>
+      <c r="N87" s="22" t="n">
+        <v>-18.645</v>
+      </c>
+      <c r="T87" s="22" t="n">
+        <v>-10.787</v>
+      </c>
+      <c r="U87" s="22" t="n">
+        <v>-12.394</v>
+      </c>
+      <c r="V87" s="22" t="n">
+        <v>-16.3</v>
+      </c>
+      <c r="W87" s="22" t="n">
+        <v>-16.938</v>
+      </c>
+      <c r="X87" s="22" t="n">
+        <v>-18.645</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C88" s="22" t="n">
-        <v>0.907</v>
-      </c>
-      <c r="D88" s="22" t="n">
-        <v>1.511</v>
+          <t>배당금수익</t>
+        </is>
       </c>
       <c r="E88" s="22" t="n">
-        <v>-0.416</v>
+        <v>0</v>
+      </c>
+      <c r="F88" s="22" t="n">
+        <v>3.297</v>
       </c>
       <c r="G88" s="22" t="n">
-        <v>0.295</v>
+        <v>0</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>1.618</v>
+        <v>3.403</v>
       </c>
       <c r="I88" s="22" t="n">
-        <v>0.699</v>
+        <v>0</v>
+      </c>
+      <c r="J88" s="22" t="n">
+        <v>4.88</v>
       </c>
       <c r="K88" s="22" t="n">
-        <v>2.105</v>
+        <v>0.016</v>
       </c>
       <c r="L88" s="22" t="n">
-        <v>1.148</v>
+        <v>4.93</v>
       </c>
       <c r="M88" s="22" t="n">
-        <v>0.597</v>
+        <v>0</v>
+      </c>
+      <c r="N88" s="22" t="n">
+        <v>6.097</v>
+      </c>
+      <c r="T88" s="22" t="n">
+        <v>3.124</v>
+      </c>
+      <c r="U88" s="22" t="n">
+        <v>2.966</v>
+      </c>
+      <c r="V88" s="22" t="n">
+        <v>3.297</v>
+      </c>
+      <c r="W88" s="22" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="X88" s="22" t="n">
+        <v>6.097</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
+          <t>매입할인</t>
         </is>
       </c>
       <c r="C89" s="22" t="n">
-        <v>9.933999999999999</v>
+        <v>1.523</v>
       </c>
       <c r="D89" s="22" t="n">
-        <v>10.499</v>
+        <v>1.64</v>
       </c>
       <c r="E89" s="22" t="n">
-        <v>9.257</v>
+        <v>1.575</v>
       </c>
       <c r="F89" s="22" t="n">
-        <v>14.021</v>
+        <v>1.251</v>
       </c>
       <c r="G89" s="22" t="n">
-        <v>12.043</v>
+        <v>1.335</v>
       </c>
       <c r="H89" s="22" t="n">
-        <v>12.311</v>
+        <v>1.642</v>
       </c>
       <c r="I89" s="22" t="n">
-        <v>10.732</v>
+        <v>1.699</v>
       </c>
       <c r="J89" s="22" t="n">
-        <v>19.56</v>
+        <v>1.529</v>
       </c>
       <c r="K89" s="22" t="n">
-        <v>16.743</v>
+        <v>1.794</v>
       </c>
       <c r="L89" s="22" t="n">
-        <v>22.22</v>
+        <v>1.942</v>
       </c>
       <c r="M89" s="22" t="n">
-        <v>16.38</v>
+        <v>1.963</v>
       </c>
       <c r="N89" s="22" t="n">
-        <v>24.659</v>
+        <v>1.962</v>
       </c>
       <c r="T89" s="22" t="n">
-        <v>12.618</v>
+        <v>1.337</v>
       </c>
       <c r="U89" s="22" t="n">
-        <v>12.056</v>
+        <v>1.363</v>
       </c>
       <c r="V89" s="22" t="n">
-        <v>14.021</v>
+        <v>1.251</v>
       </c>
       <c r="W89" s="22" t="n">
-        <v>19.56</v>
+        <v>1.529</v>
       </c>
       <c r="X89" s="22" t="n">
-        <v>24.659</v>
+        <v>1.962</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각손실</t>
+          <t>외환차익</t>
         </is>
       </c>
       <c r="C90" s="22" t="n">
-        <v>0</v>
+        <v>1.877</v>
       </c>
       <c r="D90" s="22" t="n">
-        <v>0</v>
+        <v>-1.877</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="F90" s="22" t="n">
-        <v>0</v>
+        <v>2.996</v>
+      </c>
+      <c r="G90" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="22" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="L90" s="22" t="n">
+        <v>2.397</v>
+      </c>
+      <c r="M90" s="22" t="n">
+        <v>1.076</v>
+      </c>
+      <c r="N90" s="22" t="n">
+        <v>0.8149999999999999</v>
       </c>
       <c r="T90" s="22" t="n">
-        <v>0</v>
+        <v>4.098</v>
       </c>
       <c r="U90" s="22" t="n">
-        <v>0</v>
+        <v>4.457</v>
       </c>
       <c r="V90" s="22" t="n">
-        <v>0</v>
+        <v>2.996</v>
+      </c>
+      <c r="W90" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X90" s="22" t="n">
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>외환차손</t>
+          <t>대손충당금 환입</t>
         </is>
       </c>
       <c r="C91" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D91" s="22" t="n">
-        <v>0.922</v>
-      </c>
-      <c r="E91" s="22" t="n">
-        <v>-0.922</v>
-      </c>
-      <c r="F91" s="22" t="n">
-        <v>0</v>
-      </c>
       <c r="G91" s="22" t="n">
-        <v>5.081</v>
-      </c>
-      <c r="H91" s="22" t="n">
-        <v>-4.831</v>
-      </c>
-      <c r="I91" s="22" t="n">
-        <v>2.595</v>
-      </c>
-      <c r="J91" s="22" t="n">
-        <v>1.561</v>
+        <v>3.132</v>
       </c>
       <c r="K91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W91" s="22" t="n">
-        <v>1.561</v>
-      </c>
-      <c r="X91" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>대손충당금 전입</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C92" s="22" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="D92" s="22" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="E92" s="22" t="n">
+        <v>-0.416</v>
       </c>
       <c r="G92" s="22" t="n">
-        <v>0</v>
+        <v>0.295</v>
       </c>
       <c r="H92" s="22" t="n">
-        <v>0</v>
+        <v>1.618</v>
       </c>
       <c r="I92" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="22" t="n">
-        <v>0</v>
+        <v>0.699</v>
       </c>
       <c r="K92" s="22" t="n">
-        <v>0.509</v>
+        <v>2.105</v>
       </c>
       <c r="L92" s="22" t="n">
-        <v>0.21</v>
+        <v>1.148</v>
       </c>
       <c r="M92" s="22" t="n">
-        <v>2.566</v>
-      </c>
-      <c r="N92" s="22" t="n">
-        <v>-1.134</v>
-      </c>
-      <c r="T92" s="22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U92" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W92" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X92" s="22" t="n">
-        <v>-1.134</v>
+        <v>0.597</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>잡손실</t>
+          <t>영업외수익 합계</t>
         </is>
       </c>
       <c r="C93" s="22" t="n">
-        <v>0.508</v>
+        <v>9.933999999999999</v>
       </c>
       <c r="D93" s="22" t="n">
-        <v>0.845</v>
+        <v>10.499</v>
       </c>
       <c r="E93" s="22" t="n">
-        <v>0.8179999999999999</v>
+        <v>9.257</v>
       </c>
       <c r="F93" s="22" t="n">
-        <v>0.726</v>
+        <v>14.021</v>
       </c>
       <c r="G93" s="22" t="n">
-        <v>0.833</v>
+        <v>12.043</v>
       </c>
       <c r="H93" s="22" t="n">
-        <v>1.009</v>
+        <v>12.311</v>
       </c>
       <c r="I93" s="22" t="n">
-        <v>1.397</v>
+        <v>10.732</v>
       </c>
       <c r="J93" s="22" t="n">
-        <v>1.203</v>
+        <v>19.56</v>
       </c>
       <c r="K93" s="22" t="n">
-        <v>1.129</v>
+        <v>16.743</v>
       </c>
       <c r="L93" s="22" t="n">
-        <v>1.118</v>
+        <v>22.22</v>
       </c>
       <c r="M93" s="22" t="n">
-        <v>0.574</v>
+        <v>16.38</v>
       </c>
       <c r="N93" s="22" t="n">
-        <v>0.005</v>
+        <v>24.659</v>
+      </c>
+      <c r="T93" s="22" t="n">
+        <v>12.618</v>
       </c>
       <c r="U93" s="22" t="n">
-        <v>0</v>
+        <v>12.056</v>
       </c>
       <c r="V93" s="22" t="n">
-        <v>0.726</v>
+        <v>14.021</v>
       </c>
       <c r="W93" s="22" t="n">
-        <v>1.203</v>
+        <v>19.56</v>
       </c>
       <c r="X93" s="22" t="n">
-        <v>0.005</v>
+        <v>24.659</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
+          <t>투자유가증권 매각손실</t>
         </is>
       </c>
       <c r="C94" s="22" t="n">
-        <v>0.508</v>
+        <v>0</v>
       </c>
       <c r="D94" s="22" t="n">
-        <v>1.767</v>
+        <v>0</v>
       </c>
       <c r="E94" s="22" t="n">
-        <v>-0.104</v>
+        <v>0</v>
       </c>
       <c r="F94" s="22" t="n">
-        <v>3.111</v>
-      </c>
-      <c r="G94" s="22" t="n">
-        <v>5.915</v>
-      </c>
-      <c r="H94" s="22" t="n">
-        <v>-3.822</v>
-      </c>
-      <c r="I94" s="22" t="n">
-        <v>3.992</v>
-      </c>
-      <c r="J94" s="22" t="n">
-        <v>2.763</v>
-      </c>
-      <c r="K94" s="22" t="n">
-        <v>1.639</v>
-      </c>
-      <c r="L94" s="22" t="n">
-        <v>1.327</v>
-      </c>
-      <c r="M94" s="22" t="n">
-        <v>3.141</v>
-      </c>
-      <c r="N94" s="22" t="n">
-        <v>-1.129</v>
+        <v>0</v>
       </c>
       <c r="T94" s="22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="U94" s="22" t="n">
         <v>0</v>
       </c>
       <c r="V94" s="22" t="n">
-        <v>3.111</v>
-      </c>
-      <c r="W94" s="22" t="n">
-        <v>2.763</v>
-      </c>
-      <c r="X94" s="22" t="n">
-        <v>-1.129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C95" s="12" t="n">
-        <v>83.946</v>
-      </c>
-      <c r="D95" s="12" t="n">
-        <v>161.65</v>
-      </c>
-      <c r="E95" s="12" t="n">
-        <v>67.736</v>
-      </c>
-      <c r="F95" s="12" t="n">
-        <v>58.598</v>
-      </c>
-      <c r="G95" s="12" t="n">
-        <v>97.41</v>
-      </c>
-      <c r="H95" s="12" t="n">
-        <v>238.794</v>
-      </c>
-      <c r="I95" s="12" t="n">
-        <v>121.654</v>
-      </c>
-      <c r="J95" s="12" t="n">
-        <v>103.416</v>
-      </c>
-      <c r="K95" s="12" t="n">
-        <v>103.218</v>
-      </c>
-      <c r="L95" s="12" t="n">
-        <v>211.324</v>
-      </c>
-      <c r="M95" s="12" t="n">
-        <v>119.3</v>
-      </c>
-      <c r="N95" s="12" t="n">
-        <v>133.015</v>
-      </c>
-      <c r="T95" s="12" t="n">
-        <v>80.488</v>
-      </c>
-      <c r="U95" s="12" t="n">
-        <v>55.049</v>
-      </c>
-      <c r="V95" s="12" t="n">
-        <v>58.598</v>
-      </c>
-      <c r="W95" s="12" t="n">
-        <v>103.416</v>
-      </c>
-      <c r="X95" s="12" t="n">
-        <v>133.015</v>
+      <c r="A95" s="20" t="inlineStr">
+        <is>
+          <t>외환차손</t>
+        </is>
+      </c>
+      <c r="C95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="22" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="E95" s="22" t="n">
+        <v>-0.922</v>
+      </c>
+      <c r="F95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="22" t="n">
+        <v>5.081</v>
+      </c>
+      <c r="H95" s="22" t="n">
+        <v>-4.831</v>
+      </c>
+      <c r="I95" s="22" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="J95" s="22" t="n">
+        <v>1.561</v>
+      </c>
+      <c r="K95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" s="22" t="n">
+        <v>1.561</v>
+      </c>
+      <c r="X95" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="20" t="inlineStr">
         <is>
-          <t>특별이익</t>
-        </is>
-      </c>
-      <c r="C96" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" s="22" t="n">
-        <v>0</v>
+          <t>대손충당금 전입</t>
+        </is>
       </c>
       <c r="G96" s="22" t="n">
         <v>0</v>
@@ -6762,1955 +6815,2033 @@
         <v>0</v>
       </c>
       <c r="K96" s="22" t="n">
-        <v>0</v>
+        <v>0.509</v>
       </c>
       <c r="L96" s="22" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="M96" s="22" t="n">
-        <v>0</v>
+        <v>2.566</v>
       </c>
       <c r="N96" s="22" t="n">
-        <v>0</v>
+        <v>-1.134</v>
       </c>
       <c r="T96" s="22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U96" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="22" t="n">
-        <v>0</v>
-      </c>
       <c r="W96" s="22" t="n">
         <v>0</v>
       </c>
       <c r="X96" s="22" t="n">
-        <v>0</v>
+        <v>-1.134</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각손실</t>
-        </is>
+          <t>잡손실</t>
+        </is>
+      </c>
+      <c r="C97" s="22" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="D97" s="22" t="n">
+        <v>0.845</v>
       </c>
       <c r="E97" s="22" t="n">
-        <v>0</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="F97" s="22" t="n">
-        <v>0</v>
+        <v>0.726</v>
+      </c>
+      <c r="G97" s="22" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="H97" s="22" t="n">
+        <v>1.009</v>
       </c>
       <c r="I97" s="22" t="n">
-        <v>0</v>
+        <v>1.397</v>
       </c>
       <c r="J97" s="22" t="n">
-        <v>0</v>
+        <v>1.203</v>
+      </c>
+      <c r="K97" s="22" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="L97" s="22" t="n">
+        <v>1.118</v>
       </c>
       <c r="M97" s="22" t="n">
-        <v>0</v>
+        <v>0.574</v>
       </c>
       <c r="N97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T97" s="22" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="U97" s="22" t="n">
         <v>0</v>
       </c>
       <c r="V97" s="22" t="n">
-        <v>0</v>
+        <v>0.726</v>
       </c>
       <c r="W97" s="22" t="n">
-        <v>0</v>
+        <v>1.203</v>
       </c>
       <c r="X97" s="22" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="20" t="inlineStr">
         <is>
-          <t>Company Funeral Expenses EL</t>
-        </is>
+          <t>영업외비용 합계</t>
+        </is>
+      </c>
+      <c r="C98" s="22" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="D98" s="22" t="n">
+        <v>1.767</v>
       </c>
       <c r="E98" s="22" t="n">
-        <v>0</v>
+        <v>-0.104</v>
       </c>
       <c r="F98" s="22" t="n">
-        <v>0</v>
+        <v>3.111</v>
+      </c>
+      <c r="G98" s="22" t="n">
+        <v>5.915</v>
+      </c>
+      <c r="H98" s="22" t="n">
+        <v>-3.822</v>
+      </c>
+      <c r="I98" s="22" t="n">
+        <v>3.992</v>
+      </c>
+      <c r="J98" s="22" t="n">
+        <v>2.763</v>
+      </c>
+      <c r="K98" s="22" t="n">
+        <v>1.639</v>
+      </c>
+      <c r="L98" s="22" t="n">
+        <v>1.327</v>
+      </c>
+      <c r="M98" s="22" t="n">
+        <v>3.141</v>
+      </c>
+      <c r="N98" s="22" t="n">
+        <v>-1.129</v>
       </c>
       <c r="T98" s="22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U98" s="22" t="n">
         <v>0</v>
       </c>
       <c r="V98" s="22" t="n">
-        <v>0</v>
+        <v>3.111</v>
+      </c>
+      <c r="W98" s="22" t="n">
+        <v>2.763</v>
+      </c>
+      <c r="X98" s="22" t="n">
+        <v>-1.129</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="20" t="inlineStr">
-        <is>
-          <t>특별손실 합계</t>
-        </is>
-      </c>
-      <c r="C99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" s="22" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="I99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X99" s="22" t="n">
-        <v>0</v>
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="n">
+        <v>83.946</v>
+      </c>
+      <c r="D99" s="12" t="n">
+        <v>161.65</v>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v>67.736</v>
+      </c>
+      <c r="F99" s="12" t="n">
+        <v>58.598</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>97.41</v>
+      </c>
+      <c r="H99" s="12" t="n">
+        <v>238.794</v>
+      </c>
+      <c r="I99" s="12" t="n">
+        <v>121.654</v>
+      </c>
+      <c r="J99" s="12" t="n">
+        <v>103.416</v>
+      </c>
+      <c r="K99" s="12" t="n">
+        <v>103.218</v>
+      </c>
+      <c r="L99" s="12" t="n">
+        <v>211.324</v>
+      </c>
+      <c r="M99" s="12" t="n">
+        <v>119.3</v>
+      </c>
+      <c r="N99" s="12" t="n">
+        <v>133.015</v>
+      </c>
+      <c r="T99" s="12" t="n">
+        <v>80.488</v>
+      </c>
+      <c r="U99" s="12" t="n">
+        <v>55.049</v>
+      </c>
+      <c r="V99" s="12" t="n">
+        <v>58.598</v>
+      </c>
+      <c r="W99" s="12" t="n">
+        <v>103.416</v>
+      </c>
+      <c r="X99" s="12" t="n">
+        <v>133.015</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C100" s="12" t="n">
-        <v>83.946</v>
-      </c>
-      <c r="D100" s="12" t="n">
-        <v>161.65</v>
-      </c>
-      <c r="E100" s="12" t="n">
-        <v>67.736</v>
-      </c>
-      <c r="F100" s="12" t="n">
-        <v>58.598</v>
-      </c>
-      <c r="G100" s="12" t="n">
-        <v>97.41</v>
-      </c>
-      <c r="H100" s="12" t="n">
-        <v>238.014</v>
-      </c>
-      <c r="I100" s="12" t="n">
-        <v>121.654</v>
-      </c>
-      <c r="J100" s="12" t="n">
-        <v>103.416</v>
-      </c>
-      <c r="K100" s="12" t="n">
-        <v>103.218</v>
-      </c>
-      <c r="L100" s="12" t="n">
-        <v>211.324</v>
-      </c>
-      <c r="M100" s="12" t="n">
-        <v>119.3</v>
-      </c>
-      <c r="N100" s="12" t="n">
-        <v>133.015</v>
-      </c>
-      <c r="T100" s="12" t="n">
-        <v>80.488</v>
-      </c>
-      <c r="U100" s="12" t="n">
-        <v>55.049</v>
-      </c>
-      <c r="V100" s="12" t="n">
-        <v>58.598</v>
-      </c>
-      <c r="W100" s="12" t="n">
-        <v>103.416</v>
-      </c>
-      <c r="X100" s="12" t="n">
-        <v>133.015</v>
+      <c r="A100" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G100" s="17">
+        <f>IF(OR(G99="",C99=""),"",IF(C99&lt;=0,"",IFERROR(G99/C99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H100" s="17">
+        <f>IF(OR(H99="",D99=""),"",IF(D99&lt;=0,"",IFERROR(H99/D99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I100" s="17">
+        <f>IF(OR(I99="",E99=""),"",IF(E99&lt;=0,"",IFERROR(I99/E99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J100" s="17">
+        <f>IF(OR(J99="",F99=""),"",IF(F99&lt;=0,"",IFERROR(J99/F99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K100" s="17">
+        <f>IF(OR(K99="",G99=""),"",IF(G99&lt;=0,"",IFERROR(K99/G99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L100" s="17">
+        <f>IF(OR(L99="",H99=""),"",IF(H99&lt;=0,"",IFERROR(L99/H99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M100" s="17">
+        <f>IF(OR(M99="",I99=""),"",IF(I99&lt;=0,"",IFERROR(M99/I99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N100" s="17">
+        <f>IF(OR(N99="",J99=""),"",IF(J99&lt;=0,"",IFERROR(N99/J99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T100" s="17">
+        <f>IF(OR(T99="",S99=""),"",IF(S99&lt;=0,"",IFERROR(T99/S99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U100" s="17">
+        <f>IF(OR(U99="",T99=""),"",IF(T99&lt;=0,"",IFERROR(U99/T99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V100" s="17">
+        <f>IF(OR(V99="",U99=""),"",IF(U99&lt;=0,"",IFERROR(V99/U99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W100" s="17">
+        <f>IF(OR(W99="",V99=""),"",IF(V99&lt;=0,"",IFERROR(W99/V99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X100" s="17">
+        <f>IF(OR(X99="",W99=""),"",IF(W99&lt;=0,"",IFERROR(X99/W99-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="20" t="inlineStr">
         <is>
-          <t>법인세·주민세·사업세</t>
+          <t>특별이익</t>
         </is>
       </c>
       <c r="C101" s="22" t="n">
-        <v>52.115</v>
+        <v>0</v>
       </c>
       <c r="D101" s="22" t="n">
-        <v>42.529</v>
+        <v>0</v>
       </c>
       <c r="E101" s="22" t="n">
-        <v>21.932</v>
+        <v>0</v>
       </c>
       <c r="F101" s="22" t="n">
-        <v>10.898</v>
+        <v>0</v>
       </c>
       <c r="G101" s="22" t="n">
-        <v>33.303</v>
+        <v>0</v>
       </c>
       <c r="H101" s="22" t="n">
-        <v>64.60299999999999</v>
+        <v>0</v>
       </c>
       <c r="I101" s="22" t="n">
-        <v>51.254</v>
+        <v>0</v>
       </c>
       <c r="J101" s="22" t="n">
-        <v>17.505</v>
+        <v>0</v>
       </c>
       <c r="K101" s="22" t="n">
-        <v>39.789</v>
+        <v>0</v>
       </c>
       <c r="L101" s="22" t="n">
-        <v>56.294</v>
+        <v>0</v>
       </c>
       <c r="M101" s="22" t="n">
-        <v>48.655</v>
+        <v>0</v>
       </c>
       <c r="N101" s="22" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="T101" s="22" t="n">
-        <v>11.719</v>
+        <v>0</v>
       </c>
       <c r="U101" s="22" t="n">
-        <v>-1.965</v>
+        <v>0</v>
       </c>
       <c r="V101" s="22" t="n">
-        <v>10.898</v>
+        <v>0</v>
       </c>
       <c r="W101" s="22" t="n">
-        <v>17.505</v>
+        <v>0</v>
       </c>
       <c r="X101" s="22" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="20" t="inlineStr">
         <is>
-          <t>법인세 조정액</t>
-        </is>
-      </c>
-      <c r="C102" s="22" t="n">
-        <v>-17.848</v>
-      </c>
-      <c r="D102" s="22" t="n">
-        <v>13.59</v>
+          <t>고정자산 제각손실</t>
+        </is>
       </c>
       <c r="E102" s="22" t="n">
-        <v>-16.982</v>
+        <v>0</v>
       </c>
       <c r="F102" s="22" t="n">
-        <v>10.994</v>
-      </c>
-      <c r="G102" s="22" t="n">
-        <v>-4.391</v>
-      </c>
-      <c r="H102" s="22" t="n">
-        <v>14.255</v>
+        <v>0</v>
       </c>
       <c r="I102" s="22" t="n">
-        <v>-18.555</v>
+        <v>0</v>
       </c>
       <c r="J102" s="22" t="n">
-        <v>11.662</v>
-      </c>
-      <c r="K102" s="22" t="n">
-        <v>-9.411</v>
-      </c>
-      <c r="L102" s="22" t="n">
-        <v>12.867</v>
+        <v>0</v>
       </c>
       <c r="M102" s="22" t="n">
-        <v>-15.222</v>
+        <v>0</v>
       </c>
       <c r="N102" s="22" t="n">
-        <v>0.427</v>
+        <v>0</v>
       </c>
       <c r="T102" s="22" t="n">
-        <v>15.376</v>
+        <v>0</v>
       </c>
       <c r="U102" s="22" t="n">
-        <v>15.099</v>
+        <v>0</v>
       </c>
       <c r="V102" s="22" t="n">
-        <v>10.994</v>
+        <v>0</v>
       </c>
       <c r="W102" s="22" t="n">
-        <v>11.662</v>
+        <v>0</v>
       </c>
       <c r="X102" s="22" t="n">
-        <v>0.427</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="20" t="inlineStr">
         <is>
+          <t>Company Funeral Expenses EL</t>
+        </is>
+      </c>
+      <c r="E103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="20" t="inlineStr">
+        <is>
+          <t>특별손실 합계</t>
+        </is>
+      </c>
+      <c r="C104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="22" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="n">
+        <v>83.946</v>
+      </c>
+      <c r="D105" s="12" t="n">
+        <v>161.65</v>
+      </c>
+      <c r="E105" s="12" t="n">
+        <v>67.736</v>
+      </c>
+      <c r="F105" s="12" t="n">
+        <v>58.598</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>97.41</v>
+      </c>
+      <c r="H105" s="12" t="n">
+        <v>238.014</v>
+      </c>
+      <c r="I105" s="12" t="n">
+        <v>121.654</v>
+      </c>
+      <c r="J105" s="12" t="n">
+        <v>103.416</v>
+      </c>
+      <c r="K105" s="12" t="n">
+        <v>103.218</v>
+      </c>
+      <c r="L105" s="12" t="n">
+        <v>211.324</v>
+      </c>
+      <c r="M105" s="12" t="n">
+        <v>119.3</v>
+      </c>
+      <c r="N105" s="12" t="n">
+        <v>133.015</v>
+      </c>
+      <c r="T105" s="12" t="n">
+        <v>80.488</v>
+      </c>
+      <c r="U105" s="12" t="n">
+        <v>55.049</v>
+      </c>
+      <c r="V105" s="12" t="n">
+        <v>58.598</v>
+      </c>
+      <c r="W105" s="12" t="n">
+        <v>103.416</v>
+      </c>
+      <c r="X105" s="12" t="n">
+        <v>133.015</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="C106" s="22" t="n">
+        <v>52.115</v>
+      </c>
+      <c r="D106" s="22" t="n">
+        <v>42.529</v>
+      </c>
+      <c r="E106" s="22" t="n">
+        <v>21.932</v>
+      </c>
+      <c r="F106" s="22" t="n">
+        <v>10.898</v>
+      </c>
+      <c r="G106" s="22" t="n">
+        <v>33.303</v>
+      </c>
+      <c r="H106" s="22" t="n">
+        <v>64.60299999999999</v>
+      </c>
+      <c r="I106" s="22" t="n">
+        <v>51.254</v>
+      </c>
+      <c r="J106" s="22" t="n">
+        <v>17.505</v>
+      </c>
+      <c r="K106" s="22" t="n">
+        <v>39.789</v>
+      </c>
+      <c r="L106" s="22" t="n">
+        <v>56.294</v>
+      </c>
+      <c r="M106" s="22" t="n">
+        <v>48.655</v>
+      </c>
+      <c r="N106" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="T106" s="22" t="n">
+        <v>11.719</v>
+      </c>
+      <c r="U106" s="22" t="n">
+        <v>-1.965</v>
+      </c>
+      <c r="V106" s="22" t="n">
+        <v>10.898</v>
+      </c>
+      <c r="W106" s="22" t="n">
+        <v>17.505</v>
+      </c>
+      <c r="X106" s="22" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="20" t="inlineStr">
+        <is>
+          <t>법인세 조정액</t>
+        </is>
+      </c>
+      <c r="C107" s="22" t="n">
+        <v>-17.848</v>
+      </c>
+      <c r="D107" s="22" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="E107" s="22" t="n">
+        <v>-16.982</v>
+      </c>
+      <c r="F107" s="22" t="n">
+        <v>10.994</v>
+      </c>
+      <c r="G107" s="22" t="n">
+        <v>-4.391</v>
+      </c>
+      <c r="H107" s="22" t="n">
+        <v>14.255</v>
+      </c>
+      <c r="I107" s="22" t="n">
+        <v>-18.555</v>
+      </c>
+      <c r="J107" s="22" t="n">
+        <v>11.662</v>
+      </c>
+      <c r="K107" s="22" t="n">
+        <v>-9.411</v>
+      </c>
+      <c r="L107" s="22" t="n">
+        <v>12.867</v>
+      </c>
+      <c r="M107" s="22" t="n">
+        <v>-15.222</v>
+      </c>
+      <c r="N107" s="22" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="T107" s="22" t="n">
+        <v>15.376</v>
+      </c>
+      <c r="U107" s="22" t="n">
+        <v>15.099</v>
+      </c>
+      <c r="V107" s="22" t="n">
+        <v>10.994</v>
+      </c>
+      <c r="W107" s="22" t="n">
+        <v>11.662</v>
+      </c>
+      <c r="X107" s="22" t="n">
+        <v>0.427</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="20" t="inlineStr">
+        <is>
           <t>법인세 등 합계</t>
         </is>
       </c>
-      <c r="C103" s="22" t="n">
+      <c r="C108" s="22" t="n">
         <v>34.266</v>
       </c>
-      <c r="D103" s="22" t="n">
+      <c r="D108" s="22" t="n">
         <v>56.12</v>
       </c>
-      <c r="E103" s="22" t="n">
+      <c r="E108" s="22" t="n">
         <v>4.949</v>
       </c>
-      <c r="F103" s="22" t="n">
+      <c r="F108" s="22" t="n">
         <v>21.892</v>
       </c>
-      <c r="G103" s="22" t="n">
+      <c r="G108" s="22" t="n">
         <v>28.911</v>
       </c>
-      <c r="H103" s="22" t="n">
+      <c r="H108" s="22" t="n">
         <v>78.86</v>
       </c>
-      <c r="I103" s="22" t="n">
+      <c r="I108" s="22" t="n">
         <v>32.698</v>
       </c>
-      <c r="J103" s="22" t="n">
+      <c r="J108" s="22" t="n">
         <v>29.167</v>
       </c>
-      <c r="K103" s="22" t="n">
+      <c r="K108" s="22" t="n">
         <v>30.378</v>
       </c>
-      <c r="L103" s="22" t="n">
+      <c r="L108" s="22" t="n">
         <v>69.161</v>
       </c>
-      <c r="M103" s="22" t="n">
+      <c r="M108" s="22" t="n">
         <v>33.432</v>
       </c>
-      <c r="N103" s="22" t="n">
+      <c r="N108" s="22" t="n">
         <v>43.427</v>
       </c>
-      <c r="T103" s="22" t="n">
+      <c r="T108" s="22" t="n">
         <v>27.095</v>
       </c>
-      <c r="U103" s="22" t="n">
+      <c r="U108" s="22" t="n">
         <v>13.136</v>
       </c>
-      <c r="V103" s="22" t="n">
+      <c r="V108" s="22" t="n">
         <v>21.892</v>
       </c>
-      <c r="W103" s="22" t="n">
+      <c r="W108" s="22" t="n">
         <v>29.167</v>
       </c>
-      <c r="X103" s="22" t="n">
+      <c r="X108" s="22" t="n">
         <v>43.427</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="9" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="C104" s="12" t="n">
+      <c r="C109" s="12" t="n">
         <v>49.68</v>
       </c>
-      <c r="D104" s="12" t="n">
+      <c r="D109" s="12" t="n">
         <v>105.53</v>
       </c>
-      <c r="E104" s="12" t="n">
+      <c r="E109" s="12" t="n">
         <v>62.786</v>
       </c>
-      <c r="F104" s="12" t="n">
+      <c r="F109" s="12" t="n">
         <v>36.706</v>
       </c>
-      <c r="G104" s="12" t="n">
+      <c r="G109" s="12" t="n">
         <v>68.498</v>
       </c>
-      <c r="H104" s="12" t="n">
+      <c r="H109" s="12" t="n">
         <v>159.155</v>
       </c>
-      <c r="I104" s="12" t="n">
+      <c r="I109" s="12" t="n">
         <v>88.955</v>
       </c>
-      <c r="J104" s="12" t="n">
+      <c r="J109" s="12" t="n">
         <v>74.249</v>
       </c>
-      <c r="K104" s="12" t="n">
+      <c r="K109" s="12" t="n">
         <v>72.839</v>
       </c>
-      <c r="L104" s="12" t="n">
+      <c r="L109" s="12" t="n">
         <v>142.164</v>
       </c>
-      <c r="M104" s="12" t="n">
+      <c r="M109" s="12" t="n">
         <v>85.867</v>
       </c>
-      <c r="N104" s="12" t="n">
+      <c r="N109" s="12" t="n">
         <v>89.589</v>
       </c>
-      <c r="T104" s="12" t="n">
+      <c r="T109" s="12" t="n">
         <v>53.393</v>
       </c>
-      <c r="U104" s="12" t="n">
+      <c r="U109" s="12" t="n">
         <v>41.914</v>
       </c>
-      <c r="V104" s="12" t="n">
+      <c r="V109" s="12" t="n">
         <v>36.706</v>
       </c>
-      <c r="W104" s="12" t="n">
+      <c r="W109" s="12" t="n">
         <v>74.249</v>
       </c>
-      <c r="X104" s="12" t="n">
+      <c r="X109" s="12" t="n">
         <v>89.589</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="18" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G110" s="17">
+        <f>IF(OR(G109="",C109=""),"",IF(C109&lt;=0,"",IFERROR(G109/C109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H110" s="17">
+        <f>IF(OR(H109="",D109=""),"",IF(D109&lt;=0,"",IFERROR(H109/D109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I110" s="17">
+        <f>IF(OR(I109="",E109=""),"",IF(E109&lt;=0,"",IFERROR(I109/E109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J110" s="17">
+        <f>IF(OR(J109="",F109=""),"",IF(F109&lt;=0,"",IFERROR(J109/F109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K110" s="17">
+        <f>IF(OR(K109="",G109=""),"",IF(G109&lt;=0,"",IFERROR(K109/G109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L110" s="17">
+        <f>IF(OR(L109="",H109=""),"",IF(H109&lt;=0,"",IFERROR(L109/H109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M110" s="17">
+        <f>IF(OR(M109="",I109=""),"",IF(I109&lt;=0,"",IFERROR(M109/I109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N110" s="17">
+        <f>IF(OR(N109="",J109=""),"",IF(J109&lt;=0,"",IFERROR(N109/J109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T110" s="17">
+        <f>IF(OR(T109="",S109=""),"",IF(S109&lt;=0,"",IFERROR(T109/S109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U110" s="17">
+        <f>IF(OR(U109="",T109=""),"",IF(T109&lt;=0,"",IFERROR(U109/T109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V110" s="17">
+        <f>IF(OR(V109="",U109=""),"",IF(U109&lt;=0,"",IFERROR(V109/U109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W110" s="17">
+        <f>IF(OR(W109="",V109=""),"",IF(V109&lt;=0,"",IFERROR(W109/V109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X110" s="17">
+        <f>IF(OR(X109="",W109=""),"",IF(W109&lt;=0,"",IFERROR(X109/W109-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="18" t="inlineStr">
         <is>
           <t>현금흐름표 · 전 항목</t>
         </is>
       </c>
-      <c r="B106" s="44" t="inlineStr">
+      <c r="B112" s="44" t="inlineStr">
         <is>
           <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
         </is>
       </c>
-      <c r="C106" s="18" t="n"/>
-      <c r="D106" s="18" t="n"/>
-      <c r="E106" s="18" t="n"/>
-      <c r="F106" s="18" t="n"/>
-      <c r="G106" s="18" t="n"/>
-      <c r="H106" s="18" t="n"/>
-      <c r="I106" s="18" t="n"/>
-      <c r="J106" s="18" t="n"/>
-      <c r="K106" s="18" t="n"/>
-      <c r="L106" s="18" t="n"/>
-      <c r="M106" s="18" t="n"/>
-      <c r="N106" s="18" t="n"/>
-      <c r="O106" s="18" t="n"/>
-      <c r="P106" s="18" t="n"/>
-      <c r="Q106" s="18" t="n"/>
-      <c r="R106" s="18" t="n"/>
-      <c r="S106" s="18" t="n"/>
-      <c r="T106" s="18" t="n"/>
-      <c r="U106" s="18" t="n"/>
-      <c r="V106" s="18" t="n"/>
-      <c r="W106" s="18" t="n"/>
-      <c r="X106" s="18" t="n"/>
-      <c r="Y106" s="18" t="n"/>
-      <c r="Z106" s="18" t="n"/>
-      <c r="AA106" s="18" t="n"/>
-      <c r="AB106" s="18" t="n"/>
-      <c r="AC106" s="18" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
+      <c r="C112" s="18" t="n"/>
+      <c r="D112" s="18" t="n"/>
+      <c r="E112" s="18" t="n"/>
+      <c r="F112" s="18" t="n"/>
+      <c r="G112" s="18" t="n"/>
+      <c r="H112" s="18" t="n"/>
+      <c r="I112" s="18" t="n"/>
+      <c r="J112" s="18" t="n"/>
+      <c r="K112" s="18" t="n"/>
+      <c r="L112" s="18" t="n"/>
+      <c r="M112" s="18" t="n"/>
+      <c r="N112" s="18" t="n"/>
+      <c r="O112" s="18" t="n"/>
+      <c r="P112" s="18" t="n"/>
+      <c r="Q112" s="18" t="n"/>
+      <c r="R112" s="18" t="n"/>
+      <c r="S112" s="18" t="n"/>
+      <c r="T112" s="18" t="n"/>
+      <c r="U112" s="18" t="n"/>
+      <c r="V112" s="18" t="n"/>
+      <c r="W112" s="18" t="n"/>
+      <c r="X112" s="18" t="n"/>
+      <c r="Y112" s="18" t="n"/>
+      <c r="Z112" s="18" t="n"/>
+      <c r="AA112" s="18" t="n"/>
+      <c r="AB112" s="18" t="n"/>
+      <c r="AC112" s="18" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B107" s="5" t="inlineStr">
+      <c r="B113" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
+      <c r="C113" s="5" t="inlineStr">
         <is>
           <t>2024.1Q</t>
         </is>
       </c>
-      <c r="D107" s="5" t="inlineStr">
+      <c r="D113" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="E107" s="5" t="inlineStr">
+      <c r="E113" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="F107" s="5" t="inlineStr">
+      <c r="F113" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="G107" s="5" t="inlineStr">
+      <c r="G113" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="H107" s="5" t="inlineStr">
+      <c r="H113" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="I107" s="5" t="inlineStr">
+      <c r="I113" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="J107" s="5" t="inlineStr">
+      <c r="J113" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="K107" s="5" t="inlineStr">
+      <c r="K113" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="L107" s="5" t="inlineStr">
+      <c r="L113" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="M107" s="5" t="inlineStr">
+      <c r="M113" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="N107" s="5" t="inlineStr">
+      <c r="N113" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="O107" s="5" t="inlineStr">
+      <c r="O113" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P107" s="5" t="inlineStr">
+      <c r="P113" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q107" s="5" t="inlineStr">
+      <c r="Q113" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R107" s="5" t="inlineStr">
+      <c r="R113" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S107" s="5" t="inlineStr">
+      <c r="S113" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T107" s="5" t="inlineStr">
+      <c r="T113" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U107" s="5" t="inlineStr">
+      <c r="U113" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V107" s="5" t="inlineStr">
+      <c r="V113" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W107" s="5" t="inlineStr">
+      <c r="W113" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X107" s="5" t="inlineStr">
+      <c r="X113" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y107" s="5" t="inlineStr">
+      <c r="Y113" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z107" s="5" t="inlineStr">
+      <c r="Z113" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA107" s="5" t="inlineStr">
+      <c r="AA113" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB107" s="5" t="inlineStr">
+      <c r="AB113" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC107" s="5" t="inlineStr">
+      <c r="AC113" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="9" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
         <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="D108" s="12" t="n">
+      <c r="D114" s="12" t="n">
         <v>245.596</v>
       </c>
-      <c r="F108" s="12" t="n">
+      <c r="F114" s="12" t="n">
         <v>371.93</v>
       </c>
-      <c r="H108" s="12" t="n">
+      <c r="H114" s="12" t="n">
         <v>335.424</v>
       </c>
-      <c r="J108" s="12" t="n">
+      <c r="J114" s="12" t="n">
         <v>560.494</v>
       </c>
-      <c r="L108" s="12" t="n">
+      <c r="L114" s="12" t="n">
         <v>314.542</v>
       </c>
-      <c r="N108" s="12" t="n">
+      <c r="N114" s="12" t="n">
         <v>566.857</v>
       </c>
-      <c r="O108" s="12" t="n">
+      <c r="O114" s="12" t="n">
         <v>560.38</v>
       </c>
-      <c r="P108" s="12" t="n">
+      <c r="P114" s="12" t="n">
         <v>655.4</v>
       </c>
-      <c r="Q108" s="12" t="n">
+      <c r="Q114" s="12" t="n">
         <v>657.7190000000001</v>
       </c>
-      <c r="R108" s="12" t="n">
+      <c r="R114" s="12" t="n">
         <v>705.754</v>
       </c>
-      <c r="S108" s="12" t="n">
+      <c r="S114" s="12" t="n">
         <v>649.251</v>
       </c>
-      <c r="T108" s="12" t="n">
+      <c r="T114" s="12" t="n">
         <v>606.441</v>
       </c>
-      <c r="U108" s="12" t="n">
+      <c r="U114" s="12" t="n">
         <v>407.305</v>
       </c>
-      <c r="V108" s="12" t="n">
+      <c r="V114" s="12" t="n">
         <v>371.93</v>
       </c>
-      <c r="W108" s="12" t="n">
+      <c r="W114" s="12" t="n">
         <v>560.494</v>
       </c>
-      <c r="X108" s="12" t="n">
+      <c r="X114" s="12" t="n">
         <v>566.857</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="20" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="D109" s="22" t="n">
-        <v>77.212</v>
-      </c>
-      <c r="F109" s="22" t="n">
-        <v>184.483</v>
-      </c>
-      <c r="H109" s="22" t="n">
-        <v>78.566</v>
-      </c>
-      <c r="J109" s="22" t="n">
-        <v>177.667</v>
-      </c>
-      <c r="L109" s="22" t="n">
-        <v>117.15</v>
-      </c>
-      <c r="N109" s="22" t="n">
-        <v>262.339</v>
-      </c>
-      <c r="O109" s="22" t="n">
-        <v>203.092</v>
-      </c>
-      <c r="P109" s="22" t="n">
-        <v>274.629</v>
-      </c>
-      <c r="Q109" s="22" t="n">
-        <v>205.782</v>
-      </c>
-      <c r="R109" s="22" t="n">
-        <v>195.397</v>
-      </c>
-      <c r="S109" s="22" t="n">
-        <v>180.283</v>
-      </c>
-      <c r="T109" s="22" t="n">
-        <v>196.476</v>
-      </c>
-      <c r="U109" s="22" t="n">
-        <v>189.626</v>
-      </c>
-      <c r="V109" s="22" t="n">
-        <v>184.483</v>
-      </c>
-      <c r="W109" s="22" t="n">
-        <v>177.667</v>
-      </c>
-      <c r="X109" s="22" t="n">
-        <v>262.339</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="20" t="inlineStr">
-        <is>
-          <t>대손충당금 증감</t>
-        </is>
-      </c>
-      <c r="D110" s="22" t="n">
-        <v>-1.196</v>
-      </c>
-      <c r="F110" s="22" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="H110" s="22" t="n">
-        <v>-0.913</v>
-      </c>
-      <c r="J110" s="22" t="n">
-        <v>-1.625</v>
-      </c>
-      <c r="L110" s="22" t="n">
-        <v>0.797</v>
-      </c>
-      <c r="N110" s="22" t="n">
-        <v>1.662</v>
-      </c>
-      <c r="O110" s="22" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="P110" s="22" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="Q110" s="22" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="R110" s="22" t="n">
-        <v>5.813</v>
-      </c>
-      <c r="S110" s="22" t="n">
-        <v>12.026</v>
-      </c>
-      <c r="T110" s="22" t="n">
-        <v>6.187</v>
-      </c>
-      <c r="U110" s="22" t="n">
-        <v>1.698</v>
-      </c>
-      <c r="V110" s="22" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="W110" s="22" t="n">
-        <v>-1.625</v>
-      </c>
-      <c r="X110" s="22" t="n">
-        <v>1.662</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="20" t="inlineStr">
-        <is>
-          <t>Increase Decrease In Allowance For Investment Loss Ope CF</t>
-        </is>
-      </c>
-      <c r="P111" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q111" s="22" t="n">
-        <v>28.933</v>
-      </c>
-      <c r="R111" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="20" t="inlineStr">
-        <is>
-          <t>퇴직급여충당금 증감액</t>
-        </is>
-      </c>
-      <c r="D112" s="22" t="n">
-        <v>1.778</v>
-      </c>
-      <c r="F112" s="22" t="n">
-        <v>2.516</v>
-      </c>
-      <c r="H112" s="22" t="n">
-        <v>-12.95</v>
-      </c>
-      <c r="J112" s="22" t="n">
-        <v>-8.311999999999999</v>
-      </c>
-      <c r="L112" s="22" t="n">
-        <v>-1.821</v>
-      </c>
-      <c r="N112" s="22" t="n">
-        <v>-1.734</v>
-      </c>
-      <c r="O112" s="22" t="n">
-        <v>9.323</v>
-      </c>
-      <c r="P112" s="22" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="Q112" s="22" t="n">
-        <v>7.902</v>
-      </c>
-      <c r="R112" s="22" t="n">
-        <v>-9.436999999999999</v>
-      </c>
-      <c r="S112" s="22" t="n">
-        <v>-9.782999999999999</v>
-      </c>
-      <c r="T112" s="22" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="U112" s="22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V112" s="22" t="n">
-        <v>2.516</v>
-      </c>
-      <c r="W112" s="22" t="n">
-        <v>-8.311999999999999</v>
-      </c>
-      <c r="X112" s="22" t="n">
-        <v>-1.734</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="20" t="inlineStr">
-        <is>
-          <t>임원 퇴직위로 충당금 증감</t>
-        </is>
-      </c>
-      <c r="D113" s="22" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="F113" s="22" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H113" s="22" t="n">
-        <v>-6.75</v>
-      </c>
-      <c r="J113" s="22" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="L113" s="22" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="N113" s="22" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O113" s="22" t="n">
-        <v>5.166</v>
-      </c>
-      <c r="P113" s="22" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="Q113" s="22" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="R113" s="22" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="S113" s="22" t="n">
-        <v>-3.27</v>
-      </c>
-      <c r="T113" s="22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="U113" s="22" t="n">
-        <v>-187.575</v>
-      </c>
-      <c r="V113" s="22" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W113" s="22" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="X113" s="22" t="n">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="20" t="inlineStr">
-        <is>
-          <t>제품보상 충당금 증감</t>
-        </is>
-      </c>
-      <c r="J114" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N114" s="22" t="n">
-        <v>17.708</v>
-      </c>
-      <c r="O114" s="22" t="n">
-        <v>-16.807</v>
-      </c>
-      <c r="P114" s="22" t="n">
-        <v>-18.481</v>
-      </c>
-      <c r="Q114" s="22" t="n">
-        <v>-27.054</v>
-      </c>
-      <c r="R114" s="22" t="n">
-        <v>-20.055</v>
-      </c>
-      <c r="S114" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W114" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X114" s="22" t="n">
-        <v>17.708</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수익</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="D115" s="22" t="n">
-        <v>-14.851</v>
+        <v>77.212</v>
       </c>
       <c r="F115" s="22" t="n">
-        <v>-30.54</v>
+        <v>184.483</v>
       </c>
       <c r="H115" s="22" t="n">
-        <v>-19.463</v>
+        <v>78.566</v>
       </c>
       <c r="J115" s="22" t="n">
-        <v>-42.765</v>
+        <v>177.667</v>
       </c>
       <c r="L115" s="22" t="n">
-        <v>-28.334</v>
+        <v>117.15</v>
       </c>
       <c r="N115" s="22" t="n">
-        <v>-62.752</v>
+        <v>262.339</v>
       </c>
       <c r="O115" s="22" t="n">
-        <v>-14.185</v>
+        <v>203.092</v>
       </c>
       <c r="P115" s="22" t="n">
-        <v>-15.857</v>
+        <v>274.629</v>
       </c>
       <c r="Q115" s="22" t="n">
-        <v>-16.191</v>
+        <v>205.782</v>
       </c>
       <c r="R115" s="22" t="n">
-        <v>-18.519</v>
+        <v>195.397</v>
       </c>
       <c r="S115" s="22" t="n">
-        <v>-20.672</v>
+        <v>180.283</v>
       </c>
       <c r="T115" s="22" t="n">
-        <v>-20.52</v>
+        <v>196.476</v>
       </c>
       <c r="U115" s="22" t="n">
-        <v>-24.31</v>
+        <v>189.626</v>
       </c>
       <c r="V115" s="22" t="n">
-        <v>-30.54</v>
+        <v>184.483</v>
       </c>
       <c r="W115" s="22" t="n">
-        <v>-42.765</v>
+        <v>177.667</v>
       </c>
       <c r="X115" s="22" t="n">
-        <v>-62.752</v>
+        <v>262.339</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="20" t="inlineStr">
         <is>
-          <t>외환차손익</t>
+          <t>대손충당금 증감</t>
         </is>
       </c>
       <c r="D116" s="22" t="n">
-        <v>2.361</v>
+        <v>-1.196</v>
       </c>
       <c r="F116" s="22" t="n">
-        <v>-4.111</v>
+        <v>0.407</v>
       </c>
       <c r="H116" s="22" t="n">
-        <v>1.262</v>
+        <v>-0.913</v>
       </c>
       <c r="J116" s="22" t="n">
-        <v>5.037</v>
+        <v>-1.625</v>
       </c>
       <c r="L116" s="22" t="n">
-        <v>-3.402</v>
+        <v>0.797</v>
       </c>
       <c r="N116" s="22" t="n">
-        <v>-5.607</v>
+        <v>1.662</v>
       </c>
       <c r="O116" s="22" t="n">
-        <v>0.062</v>
+        <v>0.002</v>
       </c>
       <c r="P116" s="22" t="n">
-        <v>0.001</v>
+        <v>0.155</v>
       </c>
       <c r="Q116" s="22" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.027</v>
       </c>
       <c r="R116" s="22" t="n">
-        <v>0.614</v>
+        <v>5.813</v>
       </c>
       <c r="S116" s="22" t="n">
-        <v>-1.896</v>
+        <v>12.026</v>
       </c>
       <c r="T116" s="22" t="n">
-        <v>-6.533</v>
+        <v>6.187</v>
       </c>
       <c r="U116" s="22" t="n">
-        <v>-2.996</v>
+        <v>1.698</v>
       </c>
       <c r="V116" s="22" t="n">
-        <v>-4.111</v>
+        <v>0.407</v>
       </c>
       <c r="W116" s="22" t="n">
-        <v>5.037</v>
+        <v>-1.625</v>
       </c>
       <c r="X116" s="22" t="n">
-        <v>-5.607</v>
+        <v>1.662</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="20" t="inlineStr">
         <is>
-          <t>고정자산 매각손익</t>
-        </is>
-      </c>
-      <c r="O117" s="22" t="n">
-        <v>1.217</v>
+          <t>Increase Decrease In Allowance For Investment Loss Ope CF</t>
+        </is>
       </c>
       <c r="P117" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" s="22" t="n">
+        <v>28.933</v>
+      </c>
+      <c r="R117" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="20" t="inlineStr">
         <is>
-          <t>유가증권 매각손익</t>
-        </is>
+          <t>퇴직급여충당금 증감액</t>
+        </is>
+      </c>
+      <c r="D118" s="22" t="n">
+        <v>1.778</v>
+      </c>
+      <c r="F118" s="22" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="H118" s="22" t="n">
+        <v>-12.95</v>
+      </c>
+      <c r="J118" s="22" t="n">
+        <v>-8.311999999999999</v>
+      </c>
+      <c r="L118" s="22" t="n">
+        <v>-1.821</v>
+      </c>
+      <c r="N118" s="22" t="n">
+        <v>-1.734</v>
+      </c>
+      <c r="O118" s="22" t="n">
+        <v>9.323</v>
+      </c>
+      <c r="P118" s="22" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="Q118" s="22" t="n">
+        <v>7.902</v>
       </c>
       <c r="R118" s="22" t="n">
-        <v>0</v>
+        <v>-9.436999999999999</v>
       </c>
       <c r="S118" s="22" t="n">
-        <v>-0.023</v>
+        <v>-9.782999999999999</v>
       </c>
       <c r="T118" s="22" t="n">
-        <v>0</v>
+        <v>0.58</v>
+      </c>
+      <c r="U118" s="22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V118" s="22" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="W118" s="22" t="n">
+        <v>-8.311999999999999</v>
+      </c>
+      <c r="X118" s="22" t="n">
+        <v>-1.734</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각손익</t>
+          <t>임원 퇴직위로 충당금 증감</t>
         </is>
       </c>
       <c r="D119" s="22" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="F119" s="22" t="n">
-        <v>0</v>
+        <v>8.5</v>
+      </c>
+      <c r="H119" s="22" t="n">
+        <v>-6.75</v>
+      </c>
+      <c r="J119" s="22" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="L119" s="22" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="N119" s="22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O119" s="22" t="n">
+        <v>5.166</v>
+      </c>
+      <c r="P119" s="22" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="Q119" s="22" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="R119" s="22" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="S119" s="22" t="n">
+        <v>-3.27</v>
       </c>
       <c r="T119" s="22" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="U119" s="22" t="n">
-        <v>0.395</v>
+        <v>-187.575</v>
       </c>
       <c r="V119" s="22" t="n">
-        <v>0</v>
+        <v>8.5</v>
+      </c>
+      <c r="W119" s="22" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="X119" s="22" t="n">
+        <v>8.5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각손실</t>
-        </is>
-      </c>
-      <c r="D120" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" s="22" t="n">
-        <v>0.78</v>
+          <t>제품보상 충당금 증감</t>
+        </is>
       </c>
       <c r="J120" s="22" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="L120" s="22" t="n">
         <v>0</v>
       </c>
       <c r="N120" s="22" t="n">
-        <v>0</v>
+        <v>17.708</v>
       </c>
       <c r="O120" s="22" t="n">
-        <v>0.322</v>
+        <v>-16.807</v>
       </c>
       <c r="P120" s="22" t="n">
-        <v>0.63</v>
+        <v>-18.481</v>
       </c>
       <c r="Q120" s="22" t="n">
-        <v>0.482</v>
+        <v>-27.054</v>
       </c>
       <c r="R120" s="22" t="n">
-        <v>0.387</v>
+        <v>-20.055</v>
       </c>
       <c r="S120" s="22" t="n">
-        <v>6.364</v>
-      </c>
-      <c r="T120" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U120" s="22" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="V120" s="22" t="n">
         <v>0</v>
       </c>
       <c r="W120" s="22" t="n">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="X120" s="22" t="n">
-        <v>0</v>
+        <v>17.708</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
+          <t>이자·배당금 수익</t>
         </is>
       </c>
       <c r="D121" s="22" t="n">
-        <v>-368.759</v>
+        <v>-14.851</v>
       </c>
       <c r="F121" s="22" t="n">
-        <v>-10.091</v>
+        <v>-30.54</v>
       </c>
       <c r="H121" s="22" t="n">
-        <v>-354.775</v>
+        <v>-19.463</v>
       </c>
       <c r="J121" s="22" t="n">
-        <v>39.453</v>
+        <v>-42.765</v>
       </c>
       <c r="L121" s="22" t="n">
-        <v>-262.63</v>
+        <v>-28.334</v>
       </c>
       <c r="N121" s="22" t="n">
-        <v>213.344</v>
+        <v>-62.752</v>
       </c>
       <c r="O121" s="22" t="n">
-        <v>-24.525</v>
+        <v>-14.185</v>
       </c>
       <c r="P121" s="22" t="n">
-        <v>-60.162</v>
+        <v>-15.857</v>
       </c>
       <c r="Q121" s="22" t="n">
-        <v>173.73</v>
+        <v>-16.191</v>
       </c>
       <c r="R121" s="22" t="n">
-        <v>260.996</v>
+        <v>-18.519</v>
       </c>
       <c r="S121" s="22" t="n">
-        <v>20.218</v>
+        <v>-20.672</v>
       </c>
       <c r="T121" s="22" t="n">
-        <v>-136.67</v>
+        <v>-20.52</v>
       </c>
       <c r="U121" s="22" t="n">
-        <v>-73.803</v>
+        <v>-24.31</v>
       </c>
       <c r="V121" s="22" t="n">
-        <v>-10.091</v>
+        <v>-30.54</v>
       </c>
       <c r="W121" s="22" t="n">
-        <v>39.453</v>
+        <v>-42.765</v>
       </c>
       <c r="X121" s="22" t="n">
-        <v>213.344</v>
+        <v>-62.752</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="20" t="inlineStr">
         <is>
-          <t>재고자산 증감</t>
+          <t>외환차손익</t>
         </is>
       </c>
       <c r="D122" s="22" t="n">
-        <v>-3.384</v>
+        <v>2.361</v>
       </c>
       <c r="F122" s="22" t="n">
-        <v>2.945</v>
+        <v>-4.111</v>
       </c>
       <c r="H122" s="22" t="n">
-        <v>-16.214</v>
+        <v>1.262</v>
       </c>
       <c r="J122" s="22" t="n">
-        <v>9.032</v>
+        <v>5.037</v>
       </c>
       <c r="L122" s="22" t="n">
-        <v>-26.99</v>
+        <v>-3.402</v>
       </c>
       <c r="N122" s="22" t="n">
-        <v>19.038</v>
+        <v>-5.607</v>
       </c>
       <c r="O122" s="22" t="n">
-        <v>104.329</v>
+        <v>0.062</v>
       </c>
       <c r="P122" s="22" t="n">
-        <v>-10.999</v>
+        <v>0.001</v>
       </c>
       <c r="Q122" s="22" t="n">
-        <v>8.201000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="R122" s="22" t="n">
-        <v>-52.986</v>
+        <v>0.614</v>
       </c>
       <c r="S122" s="22" t="n">
-        <v>88.03</v>
+        <v>-1.896</v>
       </c>
       <c r="T122" s="22" t="n">
-        <v>-119.61</v>
+        <v>-6.533</v>
       </c>
       <c r="U122" s="22" t="n">
-        <v>87.78</v>
+        <v>-2.996</v>
       </c>
       <c r="V122" s="22" t="n">
-        <v>2.945</v>
+        <v>-4.111</v>
       </c>
       <c r="W122" s="22" t="n">
-        <v>9.032</v>
+        <v>5.037</v>
       </c>
       <c r="X122" s="22" t="n">
-        <v>19.038</v>
+        <v>-5.607</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="20" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
-        </is>
-      </c>
-      <c r="D123" s="22" t="n">
-        <v>300.958</v>
-      </c>
-      <c r="F123" s="22" t="n">
-        <v>-76.688</v>
-      </c>
-      <c r="H123" s="22" t="n">
-        <v>-882.46</v>
-      </c>
-      <c r="J123" s="22" t="n">
-        <v>-1723.468</v>
-      </c>
-      <c r="L123" s="22" t="n">
-        <v>128.668</v>
-      </c>
-      <c r="N123" s="22" t="n">
-        <v>81.28100000000001</v>
+          <t>고정자산 매각손익</t>
+        </is>
       </c>
       <c r="O123" s="22" t="n">
-        <v>1580.318</v>
+        <v>1.217</v>
       </c>
       <c r="P123" s="22" t="n">
-        <v>33.262</v>
-      </c>
-      <c r="Q123" s="22" t="n">
-        <v>45.724</v>
-      </c>
-      <c r="R123" s="22" t="n">
-        <v>-204.171</v>
-      </c>
-      <c r="S123" s="22" t="n">
-        <v>70.896</v>
-      </c>
-      <c r="T123" s="22" t="n">
-        <v>221.942</v>
-      </c>
-      <c r="U123" s="22" t="n">
-        <v>44.333</v>
-      </c>
-      <c r="V123" s="22" t="n">
-        <v>-76.688</v>
-      </c>
-      <c r="W123" s="22" t="n">
-        <v>-1723.468</v>
-      </c>
-      <c r="X123" s="22" t="n">
-        <v>81.28100000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="20" t="inlineStr">
         <is>
-          <t>미지급 소비세 증감</t>
-        </is>
-      </c>
-      <c r="D124" s="22" t="n">
-        <v>-8.039</v>
-      </c>
-      <c r="F124" s="22" t="n">
-        <v>-16.437</v>
-      </c>
-      <c r="H124" s="22" t="n">
-        <v>37.537</v>
-      </c>
-      <c r="J124" s="22" t="n">
-        <v>34.536</v>
-      </c>
-      <c r="L124" s="22" t="n">
-        <v>-33.29</v>
-      </c>
-      <c r="N124" s="22" t="n">
-        <v>-43.299</v>
-      </c>
-      <c r="O124" s="22" t="n">
-        <v>10.379</v>
-      </c>
-      <c r="P124" s="22" t="n">
-        <v>-15.312</v>
-      </c>
-      <c r="Q124" s="22" t="n">
-        <v>9.566000000000001</v>
+          <t>유가증권 매각손익</t>
+        </is>
       </c>
       <c r="R124" s="22" t="n">
-        <v>-3.972</v>
+        <v>0</v>
       </c>
       <c r="S124" s="22" t="n">
-        <v>27.586</v>
+        <v>-0.023</v>
       </c>
       <c r="T124" s="22" t="n">
-        <v>-38.18</v>
-      </c>
-      <c r="U124" s="22" t="n">
-        <v>15.641</v>
-      </c>
-      <c r="V124" s="22" t="n">
-        <v>-16.437</v>
-      </c>
-      <c r="W124" s="22" t="n">
-        <v>34.536</v>
-      </c>
-      <c r="X124" s="22" t="n">
-        <v>-43.299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>투자유가증권 매각손익</t>
         </is>
       </c>
       <c r="D125" s="22" t="n">
-        <v>-1.534</v>
+        <v>0</v>
       </c>
       <c r="F125" s="22" t="n">
-        <v>63.669</v>
-      </c>
-      <c r="H125" s="22" t="n">
-        <v>-57.116</v>
-      </c>
-      <c r="J125" s="22" t="n">
-        <v>-74.39</v>
-      </c>
-      <c r="L125" s="22" t="n">
-        <v>44.517</v>
-      </c>
-      <c r="N125" s="22" t="n">
-        <v>17.864</v>
-      </c>
-      <c r="O125" s="22" t="n">
-        <v>-8.404</v>
-      </c>
-      <c r="P125" s="22" t="n">
-        <v>-14.704</v>
-      </c>
-      <c r="Q125" s="22" t="n">
-        <v>36.253</v>
-      </c>
-      <c r="R125" s="22" t="n">
-        <v>-26.813</v>
-      </c>
-      <c r="S125" s="22" t="n">
-        <v>-24.502</v>
+        <v>0</v>
       </c>
       <c r="T125" s="22" t="n">
-        <v>12.127</v>
+        <v>0</v>
       </c>
       <c r="U125" s="22" t="n">
-        <v>-28.85</v>
+        <v>0.395</v>
       </c>
       <c r="V125" s="22" t="n">
-        <v>63.669</v>
-      </c>
-      <c r="W125" s="22" t="n">
-        <v>-74.39</v>
-      </c>
-      <c r="X125" s="22" t="n">
-        <v>17.864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>고정자산 제각손실</t>
         </is>
       </c>
       <c r="D126" s="22" t="n">
-        <v>234.389</v>
+        <v>0</v>
       </c>
       <c r="F126" s="22" t="n">
-        <v>496.582</v>
+        <v>0</v>
       </c>
       <c r="H126" s="22" t="n">
-        <v>-897.073</v>
+        <v>0.78</v>
       </c>
       <c r="J126" s="22" t="n">
-        <v>-1026.059</v>
+        <v>0.78</v>
       </c>
       <c r="L126" s="22" t="n">
-        <v>253.457</v>
+        <v>0</v>
       </c>
       <c r="N126" s="22" t="n">
-        <v>1075.203</v>
+        <v>0</v>
       </c>
       <c r="O126" s="22" t="n">
-        <v>2410.672</v>
+        <v>0.322</v>
       </c>
       <c r="P126" s="22" t="n">
-        <v>846.394</v>
+        <v>0.63</v>
       </c>
       <c r="Q126" s="22" t="n">
-        <v>1142.396</v>
+        <v>0.482</v>
       </c>
       <c r="R126" s="22" t="n">
-        <v>844.258</v>
+        <v>0.387</v>
       </c>
       <c r="S126" s="22" t="n">
-        <v>994.509</v>
+        <v>6.364</v>
       </c>
       <c r="T126" s="22" t="n">
-        <v>734.741</v>
+        <v>0</v>
       </c>
       <c r="U126" s="22" t="n">
-        <v>431.032</v>
+        <v>0.115</v>
       </c>
       <c r="V126" s="22" t="n">
-        <v>496.582</v>
+        <v>0</v>
       </c>
       <c r="W126" s="22" t="n">
-        <v>-1026.059</v>
+        <v>0.78</v>
       </c>
       <c r="X126" s="22" t="n">
-        <v>1075.203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
+          <t>매출채권 증감</t>
         </is>
       </c>
       <c r="D127" s="22" t="n">
-        <v>12.73</v>
+        <v>-368.759</v>
       </c>
       <c r="F127" s="22" t="n">
-        <v>27.304</v>
+        <v>-10.091</v>
       </c>
       <c r="H127" s="22" t="n">
-        <v>17.046</v>
+        <v>-354.775</v>
       </c>
       <c r="J127" s="22" t="n">
-        <v>37.418</v>
+        <v>39.453</v>
       </c>
       <c r="L127" s="22" t="n">
-        <v>25.473</v>
+        <v>-262.63</v>
       </c>
       <c r="N127" s="22" t="n">
-        <v>56.48</v>
+        <v>213.344</v>
       </c>
       <c r="O127" s="22" t="n">
-        <v>11.826</v>
+        <v>-24.525</v>
       </c>
       <c r="P127" s="22" t="n">
-        <v>12.887</v>
+        <v>-60.162</v>
       </c>
       <c r="Q127" s="22" t="n">
-        <v>13.011</v>
+        <v>173.73</v>
       </c>
       <c r="R127" s="22" t="n">
-        <v>14.709</v>
+        <v>260.996</v>
       </c>
       <c r="S127" s="22" t="n">
-        <v>17.143</v>
+        <v>20.218</v>
       </c>
       <c r="T127" s="22" t="n">
-        <v>16.499</v>
+        <v>-136.67</v>
       </c>
       <c r="U127" s="22" t="n">
-        <v>19.087</v>
+        <v>-73.803</v>
       </c>
       <c r="V127" s="22" t="n">
-        <v>27.304</v>
+        <v>-10.091</v>
       </c>
       <c r="W127" s="22" t="n">
-        <v>37.418</v>
+        <v>39.453</v>
       </c>
       <c r="X127" s="22" t="n">
-        <v>56.48</v>
+        <v>213.344</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
-        </is>
+          <t>재고자산 증감</t>
+        </is>
+      </c>
+      <c r="D128" s="22" t="n">
+        <v>-3.384</v>
+      </c>
+      <c r="F128" s="22" t="n">
+        <v>2.945</v>
+      </c>
+      <c r="H128" s="22" t="n">
+        <v>-16.214</v>
+      </c>
+      <c r="J128" s="22" t="n">
+        <v>9.032</v>
+      </c>
+      <c r="L128" s="22" t="n">
+        <v>-26.99</v>
+      </c>
+      <c r="N128" s="22" t="n">
+        <v>19.038</v>
       </c>
       <c r="O128" s="22" t="n">
-        <v>-160.964</v>
+        <v>104.329</v>
       </c>
       <c r="P128" s="22" t="n">
-        <v>-181.693</v>
+        <v>-10.999</v>
       </c>
       <c r="Q128" s="22" t="n">
-        <v>-227.603</v>
+        <v>8.201000000000001</v>
       </c>
       <c r="R128" s="22" t="n">
-        <v>-231.984</v>
+        <v>-52.986</v>
       </c>
       <c r="S128" s="22" t="n">
-        <v>-199.197</v>
+        <v>88.03</v>
       </c>
       <c r="T128" s="22" t="n">
-        <v>-205.665</v>
+        <v>-119.61</v>
       </c>
       <c r="U128" s="22" t="n">
-        <v>-189.893</v>
+        <v>87.78</v>
+      </c>
+      <c r="V128" s="22" t="n">
+        <v>2.945</v>
+      </c>
+      <c r="W128" s="22" t="n">
+        <v>9.032</v>
+      </c>
+      <c r="X128" s="22" t="n">
+        <v>19.038</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부·환급</t>
+          <t>매입채무 증감</t>
         </is>
       </c>
       <c r="D129" s="22" t="n">
-        <v>43.633</v>
+        <v>300.958</v>
       </c>
       <c r="F129" s="22" t="n">
-        <v>16.586</v>
+        <v>-76.688</v>
       </c>
       <c r="H129" s="22" t="n">
-        <v>-101.101</v>
+        <v>-882.46</v>
       </c>
       <c r="J129" s="22" t="n">
-        <v>-165.913</v>
+        <v>-1723.468</v>
       </c>
       <c r="L129" s="22" t="n">
-        <v>-103.189</v>
+        <v>128.668</v>
       </c>
       <c r="N129" s="22" t="n">
-        <v>-188.447</v>
+        <v>81.28100000000001</v>
+      </c>
+      <c r="O129" s="22" t="n">
+        <v>1580.318</v>
+      </c>
+      <c r="P129" s="22" t="n">
+        <v>33.262</v>
+      </c>
+      <c r="Q129" s="22" t="n">
+        <v>45.724</v>
+      </c>
+      <c r="R129" s="22" t="n">
+        <v>-204.171</v>
+      </c>
+      <c r="S129" s="22" t="n">
+        <v>70.896</v>
+      </c>
+      <c r="T129" s="22" t="n">
+        <v>221.942</v>
       </c>
       <c r="U129" s="22" t="n">
-        <v>-189.893</v>
+        <v>44.333</v>
       </c>
       <c r="V129" s="22" t="n">
-        <v>16.586</v>
+        <v>-76.688</v>
       </c>
       <c r="W129" s="22" t="n">
-        <v>-165.913</v>
+        <v>-1723.468</v>
       </c>
       <c r="X129" s="22" t="n">
-        <v>-188.447</v>
+        <v>81.28100000000001</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="D130" s="12" t="n">
-        <v>290.754</v>
-      </c>
-      <c r="F130" s="12" t="n">
-        <v>540.473</v>
-      </c>
-      <c r="H130" s="12" t="n">
-        <v>-981.129</v>
-      </c>
-      <c r="J130" s="12" t="n">
-        <v>-1154.554</v>
-      </c>
-      <c r="L130" s="12" t="n">
-        <v>175.74</v>
-      </c>
-      <c r="N130" s="12" t="n">
-        <v>943.236</v>
-      </c>
-      <c r="O130" s="12" t="n">
-        <v>2261.534</v>
-      </c>
-      <c r="P130" s="12" t="n">
-        <v>677.5890000000001</v>
-      </c>
-      <c r="Q130" s="12" t="n">
-        <v>927.8049999999999</v>
-      </c>
-      <c r="R130" s="12" t="n">
-        <v>626.984</v>
-      </c>
-      <c r="S130" s="12" t="n">
-        <v>812.456</v>
-      </c>
-      <c r="T130" s="12" t="n">
-        <v>545.575</v>
-      </c>
-      <c r="U130" s="12" t="n">
-        <v>260.226</v>
-      </c>
-      <c r="V130" s="12" t="n">
-        <v>540.473</v>
-      </c>
-      <c r="W130" s="12" t="n">
-        <v>-1154.554</v>
-      </c>
-      <c r="X130" s="12" t="n">
-        <v>943.236</v>
+      <c r="A130" s="20" t="inlineStr">
+        <is>
+          <t>미지급 소비세 증감</t>
+        </is>
+      </c>
+      <c r="D130" s="22" t="n">
+        <v>-8.039</v>
+      </c>
+      <c r="F130" s="22" t="n">
+        <v>-16.437</v>
+      </c>
+      <c r="H130" s="22" t="n">
+        <v>37.537</v>
+      </c>
+      <c r="J130" s="22" t="n">
+        <v>34.536</v>
+      </c>
+      <c r="L130" s="22" t="n">
+        <v>-33.29</v>
+      </c>
+      <c r="N130" s="22" t="n">
+        <v>-43.299</v>
+      </c>
+      <c r="O130" s="22" t="n">
+        <v>10.379</v>
+      </c>
+      <c r="P130" s="22" t="n">
+        <v>-15.312</v>
+      </c>
+      <c r="Q130" s="22" t="n">
+        <v>9.566000000000001</v>
+      </c>
+      <c r="R130" s="22" t="n">
+        <v>-3.972</v>
+      </c>
+      <c r="S130" s="22" t="n">
+        <v>27.586</v>
+      </c>
+      <c r="T130" s="22" t="n">
+        <v>-38.18</v>
+      </c>
+      <c r="U130" s="22" t="n">
+        <v>15.641</v>
+      </c>
+      <c r="V130" s="22" t="n">
+        <v>-16.437</v>
+      </c>
+      <c r="W130" s="22" t="n">
+        <v>34.536</v>
+      </c>
+      <c r="X130" s="22" t="n">
+        <v>-43.299</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>정기예금 예입</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="D131" s="22" t="n">
-        <v>0</v>
+        <v>-1.534</v>
       </c>
       <c r="F131" s="22" t="n">
-        <v>0</v>
+        <v>63.669</v>
       </c>
       <c r="H131" s="22" t="n">
-        <v>-1500</v>
+        <v>-57.116</v>
       </c>
       <c r="J131" s="22" t="n">
-        <v>-5100</v>
+        <v>-74.39</v>
       </c>
       <c r="L131" s="22" t="n">
-        <v>-3100</v>
+        <v>44.517</v>
       </c>
       <c r="N131" s="22" t="n">
-        <v>-7000</v>
+        <v>17.864</v>
+      </c>
+      <c r="O131" s="22" t="n">
+        <v>-8.404</v>
+      </c>
+      <c r="P131" s="22" t="n">
+        <v>-14.704</v>
+      </c>
+      <c r="Q131" s="22" t="n">
+        <v>36.253</v>
+      </c>
+      <c r="R131" s="22" t="n">
+        <v>-26.813</v>
+      </c>
+      <c r="S131" s="22" t="n">
+        <v>-24.502</v>
+      </c>
+      <c r="T131" s="22" t="n">
+        <v>12.127</v>
+      </c>
+      <c r="U131" s="22" t="n">
+        <v>-28.85</v>
       </c>
       <c r="V131" s="22" t="n">
-        <v>0</v>
+        <v>63.669</v>
       </c>
       <c r="W131" s="22" t="n">
-        <v>-5100</v>
+        <v>-74.39</v>
       </c>
       <c r="X131" s="22" t="n">
-        <v>-7000</v>
+        <v>17.864</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>정기예금 인출</t>
+          <t>소계</t>
         </is>
       </c>
       <c r="D132" s="22" t="n">
-        <v>0</v>
+        <v>234.389</v>
       </c>
       <c r="F132" s="22" t="n">
-        <v>0</v>
+        <v>496.582</v>
       </c>
       <c r="H132" s="22" t="n">
-        <v>400</v>
+        <v>-897.073</v>
       </c>
       <c r="J132" s="22" t="n">
-        <v>3600</v>
+        <v>-1026.059</v>
       </c>
       <c r="L132" s="22" t="n">
-        <v>2700</v>
+        <v>253.457</v>
       </c>
       <c r="N132" s="22" t="n">
-        <v>6400</v>
+        <v>1075.203</v>
+      </c>
+      <c r="O132" s="22" t="n">
+        <v>2410.672</v>
+      </c>
+      <c r="P132" s="22" t="n">
+        <v>846.394</v>
+      </c>
+      <c r="Q132" s="22" t="n">
+        <v>1142.396</v>
+      </c>
+      <c r="R132" s="22" t="n">
+        <v>844.258</v>
+      </c>
+      <c r="S132" s="22" t="n">
+        <v>994.509</v>
+      </c>
+      <c r="T132" s="22" t="n">
+        <v>734.741</v>
+      </c>
+      <c r="U132" s="22" t="n">
+        <v>431.032</v>
       </c>
       <c r="V132" s="22" t="n">
-        <v>0</v>
+        <v>496.582</v>
       </c>
       <c r="W132" s="22" t="n">
-        <v>3600</v>
+        <v>-1026.059</v>
       </c>
       <c r="X132" s="22" t="n">
-        <v>6400</v>
+        <v>1075.203</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>유가증권 상환 수입</t>
-        </is>
+          <t>이자·배당금 수취</t>
+        </is>
+      </c>
+      <c r="D133" s="22" t="n">
+        <v>12.73</v>
       </c>
       <c r="F133" s="22" t="n">
-        <v>0</v>
+        <v>27.304</v>
       </c>
       <c r="H133" s="22" t="n">
-        <v>0</v>
+        <v>17.046</v>
       </c>
       <c r="J133" s="22" t="n">
-        <v>300</v>
+        <v>37.418</v>
       </c>
       <c r="L133" s="22" t="n">
-        <v>100</v>
+        <v>25.473</v>
       </c>
       <c r="N133" s="22" t="n">
-        <v>200</v>
+        <v>56.48</v>
       </c>
       <c r="O133" s="22" t="n">
-        <v>0</v>
+        <v>11.826</v>
       </c>
       <c r="P133" s="22" t="n">
-        <v>200</v>
+        <v>12.887</v>
       </c>
       <c r="Q133" s="22" t="n">
-        <v>100</v>
+        <v>13.011</v>
       </c>
       <c r="R133" s="22" t="n">
-        <v>0</v>
+        <v>14.709</v>
+      </c>
+      <c r="S133" s="22" t="n">
+        <v>17.143</v>
+      </c>
+      <c r="T133" s="22" t="n">
+        <v>16.499</v>
+      </c>
+      <c r="U133" s="22" t="n">
+        <v>19.087</v>
       </c>
       <c r="V133" s="22" t="n">
-        <v>0</v>
+        <v>27.304</v>
       </c>
       <c r="W133" s="22" t="n">
-        <v>300</v>
+        <v>37.418</v>
       </c>
       <c r="X133" s="22" t="n">
-        <v>200</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
-        </is>
-      </c>
-      <c r="D134" s="22" t="n">
-        <v>-74.43000000000001</v>
-      </c>
-      <c r="F134" s="22" t="n">
-        <v>-140.543</v>
-      </c>
-      <c r="H134" s="22" t="n">
-        <v>-192.847</v>
-      </c>
-      <c r="J134" s="22" t="n">
-        <v>-233.174</v>
-      </c>
-      <c r="L134" s="22" t="n">
-        <v>-73.506</v>
-      </c>
-      <c r="N134" s="22" t="n">
-        <v>-126.998</v>
+          <t>법인세 납부</t>
+        </is>
       </c>
       <c r="O134" s="22" t="n">
-        <v>-119.876</v>
+        <v>-160.964</v>
       </c>
       <c r="P134" s="22" t="n">
-        <v>-333.896</v>
+        <v>-181.693</v>
       </c>
       <c r="Q134" s="22" t="n">
-        <v>-386.608</v>
+        <v>-227.603</v>
       </c>
       <c r="R134" s="22" t="n">
-        <v>-249.47</v>
+        <v>-231.984</v>
       </c>
       <c r="S134" s="22" t="n">
-        <v>-140.589</v>
+        <v>-199.197</v>
       </c>
       <c r="T134" s="22" t="n">
-        <v>-143.427</v>
+        <v>-205.665</v>
       </c>
       <c r="U134" s="22" t="n">
-        <v>-113.511</v>
-      </c>
-      <c r="V134" s="22" t="n">
-        <v>-140.543</v>
-      </c>
-      <c r="W134" s="22" t="n">
-        <v>-233.174</v>
-      </c>
-      <c r="X134" s="22" t="n">
-        <v>-126.998</v>
+        <v>-189.893</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
+          <t>법인세 납부·환급</t>
         </is>
       </c>
       <c r="D135" s="22" t="n">
-        <v>-0.55</v>
+        <v>43.633</v>
       </c>
       <c r="F135" s="22" t="n">
-        <v>-43.55</v>
+        <v>16.586</v>
       </c>
       <c r="H135" s="22" t="n">
-        <v>-89.126</v>
+        <v>-101.101</v>
       </c>
       <c r="J135" s="22" t="n">
-        <v>-256.476</v>
+        <v>-165.913</v>
       </c>
       <c r="L135" s="22" t="n">
-        <v>-36.396</v>
+        <v>-103.189</v>
       </c>
       <c r="N135" s="22" t="n">
-        <v>-40.517</v>
-      </c>
-      <c r="O135" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" s="22" t="n">
-        <v>-6.255</v>
-      </c>
-      <c r="Q135" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" s="22" t="n">
-        <v>-26.937</v>
-      </c>
-      <c r="S135" s="22" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="T135" s="22" t="n">
-        <v>-2.2</v>
+        <v>-188.447</v>
       </c>
       <c r="U135" s="22" t="n">
-        <v>-6.56</v>
+        <v>-189.893</v>
       </c>
       <c r="V135" s="22" t="n">
-        <v>-43.55</v>
+        <v>16.586</v>
       </c>
       <c r="W135" s="22" t="n">
-        <v>-256.476</v>
+        <v>-165.913</v>
       </c>
       <c r="X135" s="22" t="n">
-        <v>-40.517</v>
+        <v>-188.447</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="20" t="inlineStr">
-        <is>
-          <t>투자유가증권 취득</t>
-        </is>
-      </c>
-      <c r="D136" s="22" t="n">
-        <v>-201.499</v>
-      </c>
-      <c r="F136" s="22" t="n">
-        <v>-402.999</v>
-      </c>
-      <c r="H136" s="22" t="n">
-        <v>-301.499</v>
-      </c>
-      <c r="J136" s="22" t="n">
-        <v>-502.999</v>
-      </c>
-      <c r="L136" s="22" t="n">
-        <v>-201.499</v>
-      </c>
-      <c r="N136" s="22" t="n">
-        <v>-502.999</v>
-      </c>
-      <c r="O136" s="22" t="n">
-        <v>-403.599</v>
-      </c>
-      <c r="P136" s="22" t="n">
-        <v>-503.599</v>
-      </c>
-      <c r="Q136" s="22" t="n">
-        <v>-303.599</v>
-      </c>
-      <c r="R136" s="22" t="n">
-        <v>-603.599</v>
-      </c>
-      <c r="S136" s="22" t="n">
-        <v>-203.599</v>
-      </c>
-      <c r="T136" s="22" t="n">
-        <v>-503.249</v>
-      </c>
-      <c r="U136" s="22" t="n">
-        <v>-602.999</v>
-      </c>
-      <c r="V136" s="22" t="n">
-        <v>-402.999</v>
-      </c>
-      <c r="W136" s="22" t="n">
-        <v>-502.999</v>
-      </c>
-      <c r="X136" s="22" t="n">
-        <v>-502.999</v>
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="D136" s="12" t="n">
+        <v>290.754</v>
+      </c>
+      <c r="F136" s="12" t="n">
+        <v>540.473</v>
+      </c>
+      <c r="H136" s="12" t="n">
+        <v>-981.129</v>
+      </c>
+      <c r="J136" s="12" t="n">
+        <v>-1154.554</v>
+      </c>
+      <c r="L136" s="12" t="n">
+        <v>175.74</v>
+      </c>
+      <c r="N136" s="12" t="n">
+        <v>943.236</v>
+      </c>
+      <c r="O136" s="12" t="n">
+        <v>2261.534</v>
+      </c>
+      <c r="P136" s="12" t="n">
+        <v>677.5890000000001</v>
+      </c>
+      <c r="Q136" s="12" t="n">
+        <v>927.8049999999999</v>
+      </c>
+      <c r="R136" s="12" t="n">
+        <v>626.984</v>
+      </c>
+      <c r="S136" s="12" t="n">
+        <v>812.456</v>
+      </c>
+      <c r="T136" s="12" t="n">
+        <v>545.575</v>
+      </c>
+      <c r="U136" s="12" t="n">
+        <v>260.226</v>
+      </c>
+      <c r="V136" s="12" t="n">
+        <v>540.473</v>
+      </c>
+      <c r="W136" s="12" t="n">
+        <v>-1154.554</v>
+      </c>
+      <c r="X136" s="12" t="n">
+        <v>943.236</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각</t>
+          <t>정기예금 예입</t>
         </is>
       </c>
       <c r="D137" s="22" t="n">
@@ -8719,561 +8850,837 @@
       <c r="F137" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="R137" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S137" s="22" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="T137" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U137" s="22" t="n">
-        <v>4.368</v>
+      <c r="H137" s="22" t="n">
+        <v>-1500</v>
+      </c>
+      <c r="J137" s="22" t="n">
+        <v>-5100</v>
+      </c>
+      <c r="L137" s="22" t="n">
+        <v>-3100</v>
+      </c>
+      <c r="N137" s="22" t="n">
+        <v>-7000</v>
       </c>
       <c r="V137" s="22" t="n">
         <v>0</v>
+      </c>
+      <c r="W137" s="22" t="n">
+        <v>-5100</v>
+      </c>
+      <c r="X137" s="22" t="n">
+        <v>-7000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 상환</t>
+          <t>정기예금 인출</t>
         </is>
       </c>
       <c r="D138" s="22" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F138" s="22" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H138" s="22" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="J138" s="22" t="n">
-        <v>300</v>
+        <v>3600</v>
       </c>
       <c r="L138" s="22" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="N138" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O138" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="P138" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q138" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="R138" s="22" t="n">
-        <v>200</v>
-      </c>
-      <c r="S138" s="22" t="n">
-        <v>52.99</v>
-      </c>
-      <c r="T138" s="22" t="n">
-        <v>500</v>
-      </c>
-      <c r="U138" s="22" t="n">
-        <v>500</v>
+        <v>6400</v>
       </c>
       <c r="V138" s="22" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="W138" s="22" t="n">
-        <v>300</v>
+        <v>3600</v>
       </c>
       <c r="X138" s="22" t="n">
-        <v>0</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>자회사 주식 취득</t>
-        </is>
+          <t>유가증권 상환 수입</t>
+        </is>
+      </c>
+      <c r="F139" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="22" t="n">
+        <v>300</v>
+      </c>
+      <c r="L139" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="N139" s="22" t="n">
+        <v>200</v>
       </c>
       <c r="O139" s="22" t="n">
-        <v>-28.933</v>
+        <v>0</v>
       </c>
       <c r="P139" s="22" t="n">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="Q139" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="R139" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W139" s="22" t="n">
+        <v>300</v>
+      </c>
+      <c r="X139" s="22" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>대여</t>
+          <t>유형자산 취득(설비투자)</t>
         </is>
       </c>
       <c r="D140" s="22" t="n">
-        <v>-20.256</v>
+        <v>-74.43000000000001</v>
       </c>
       <c r="F140" s="22" t="n">
-        <v>-33.219</v>
+        <v>-140.543</v>
       </c>
       <c r="H140" s="22" t="n">
-        <v>-19.993</v>
+        <v>-192.847</v>
       </c>
       <c r="J140" s="22" t="n">
-        <v>-40.468</v>
+        <v>-233.174</v>
       </c>
       <c r="L140" s="22" t="n">
-        <v>-15.165</v>
+        <v>-73.506</v>
       </c>
       <c r="N140" s="22" t="n">
-        <v>-38.211</v>
+        <v>-126.998</v>
+      </c>
+      <c r="O140" s="22" t="n">
+        <v>-119.876</v>
       </c>
       <c r="P140" s="22" t="n">
-        <v>0</v>
+        <v>-333.896</v>
       </c>
       <c r="Q140" s="22" t="n">
-        <v>-1</v>
+        <v>-386.608</v>
       </c>
       <c r="R140" s="22" t="n">
-        <v>-19.215</v>
+        <v>-249.47</v>
       </c>
       <c r="S140" s="22" t="n">
-        <v>-26.107</v>
+        <v>-140.589</v>
       </c>
       <c r="T140" s="22" t="n">
-        <v>-26.803</v>
+        <v>-143.427</v>
       </c>
       <c r="U140" s="22" t="n">
-        <v>-31.124</v>
+        <v>-113.511</v>
       </c>
       <c r="V140" s="22" t="n">
-        <v>-33.219</v>
+        <v>-140.543</v>
       </c>
       <c r="W140" s="22" t="n">
-        <v>-40.468</v>
+        <v>-233.174</v>
       </c>
       <c r="X140" s="22" t="n">
-        <v>-38.211</v>
+        <v>-126.998</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="20" t="inlineStr">
         <is>
-          <t>대여금 회수</t>
+          <t>무형자산 취득</t>
         </is>
       </c>
       <c r="D141" s="22" t="n">
-        <v>21.152</v>
+        <v>-0.55</v>
       </c>
       <c r="F141" s="22" t="n">
-        <v>34.86</v>
+        <v>-43.55</v>
       </c>
       <c r="H141" s="22" t="n">
-        <v>20.274</v>
+        <v>-89.126</v>
       </c>
       <c r="J141" s="22" t="n">
-        <v>36.405</v>
+        <v>-256.476</v>
       </c>
       <c r="L141" s="22" t="n">
-        <v>17.941</v>
+        <v>-36.396</v>
       </c>
       <c r="N141" s="22" t="n">
-        <v>40.862</v>
+        <v>-40.517</v>
       </c>
       <c r="O141" s="22" t="n">
-        <v>0.856</v>
+        <v>0</v>
       </c>
       <c r="P141" s="22" t="n">
-        <v>0.777</v>
+        <v>-6.255</v>
       </c>
       <c r="Q141" s="22" t="n">
-        <v>0.8110000000000001</v>
+        <v>0</v>
       </c>
       <c r="R141" s="22" t="n">
-        <v>4.565</v>
+        <v>-26.937</v>
       </c>
       <c r="S141" s="22" t="n">
-        <v>19.766</v>
+        <v>-8.5</v>
       </c>
       <c r="T141" s="22" t="n">
-        <v>24.212</v>
+        <v>-2.2</v>
       </c>
       <c r="U141" s="22" t="n">
-        <v>34.774</v>
+        <v>-6.56</v>
       </c>
       <c r="V141" s="22" t="n">
-        <v>34.86</v>
+        <v>-43.55</v>
       </c>
       <c r="W141" s="22" t="n">
-        <v>36.405</v>
+        <v>-256.476</v>
       </c>
       <c r="X141" s="22" t="n">
-        <v>40.862</v>
+        <v>-40.517</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>투자유가증권 취득</t>
         </is>
       </c>
       <c r="D142" s="22" t="n">
-        <v>0</v>
+        <v>-201.499</v>
       </c>
       <c r="F142" s="22" t="n">
-        <v>-4.33</v>
+        <v>-402.999</v>
       </c>
       <c r="H142" s="22" t="n">
-        <v>1.831</v>
+        <v>-301.499</v>
       </c>
       <c r="J142" s="22" t="n">
-        <v>1.831</v>
+        <v>-502.999</v>
       </c>
       <c r="L142" s="22" t="n">
-        <v>0</v>
+        <v>-201.499</v>
       </c>
       <c r="N142" s="22" t="n">
-        <v>0</v>
+        <v>-502.999</v>
       </c>
       <c r="O142" s="22" t="n">
-        <v>-0.051</v>
+        <v>-403.599</v>
       </c>
       <c r="P142" s="22" t="n">
-        <v>0.382</v>
+        <v>-503.599</v>
       </c>
       <c r="Q142" s="22" t="n">
-        <v>0</v>
+        <v>-303.599</v>
       </c>
       <c r="R142" s="22" t="n">
-        <v>5.231</v>
+        <v>-603.599</v>
       </c>
       <c r="S142" s="22" t="n">
-        <v>0</v>
+        <v>-203.599</v>
+      </c>
+      <c r="T142" s="22" t="n">
+        <v>-503.249</v>
       </c>
       <c r="U142" s="22" t="n">
-        <v>0</v>
+        <v>-602.999</v>
       </c>
       <c r="V142" s="22" t="n">
-        <v>-4.33</v>
+        <v>-402.999</v>
       </c>
       <c r="W142" s="22" t="n">
-        <v>1.831</v>
+        <v>-502.999</v>
       </c>
       <c r="X142" s="22" t="n">
-        <v>0</v>
+        <v>-502.999</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="D143" s="12" t="n">
-        <v>-75.584</v>
-      </c>
-      <c r="F143" s="12" t="n">
-        <v>-289.782</v>
-      </c>
-      <c r="H143" s="12" t="n">
-        <v>-1381.36</v>
-      </c>
-      <c r="J143" s="12" t="n">
-        <v>-1894.881</v>
-      </c>
-      <c r="L143" s="12" t="n">
-        <v>-608.626</v>
-      </c>
-      <c r="N143" s="12" t="n">
-        <v>-1067.863</v>
-      </c>
-      <c r="O143" s="12" t="n">
-        <v>-451.604</v>
-      </c>
-      <c r="P143" s="12" t="n">
-        <v>-542.591</v>
-      </c>
-      <c r="Q143" s="12" t="n">
-        <v>-490.396</v>
-      </c>
-      <c r="R143" s="12" t="n">
-        <v>-689.426</v>
-      </c>
-      <c r="S143" s="12" t="n">
-        <v>-306.003</v>
-      </c>
-      <c r="T143" s="12" t="n">
-        <v>-151.467</v>
-      </c>
-      <c r="U143" s="12" t="n">
-        <v>-215.052</v>
-      </c>
-      <c r="V143" s="12" t="n">
-        <v>-289.782</v>
-      </c>
-      <c r="W143" s="12" t="n">
-        <v>-1894.881</v>
-      </c>
-      <c r="X143" s="12" t="n">
-        <v>-1067.863</v>
+      <c r="A143" s="20" t="inlineStr">
+        <is>
+          <t>투자유가증권 매각</t>
+        </is>
+      </c>
+      <c r="D143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" s="22" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="T143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" s="22" t="n">
+        <v>4.368</v>
+      </c>
+      <c r="V143" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="20" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
-        </is>
+          <t>투자유가증권 상환</t>
+        </is>
+      </c>
+      <c r="D144" s="22" t="n">
+        <v>200</v>
       </c>
       <c r="F144" s="22" t="n">
-        <v>-0.058</v>
+        <v>300</v>
+      </c>
+      <c r="H144" s="22" t="n">
+        <v>300</v>
       </c>
       <c r="J144" s="22" t="n">
+        <v>300</v>
+      </c>
+      <c r="L144" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" s="22" t="n">
         <v>0</v>
       </c>
       <c r="O144" s="22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P144" s="22" t="n">
-        <v>-0.042</v>
+        <v>100</v>
       </c>
       <c r="Q144" s="22" t="n">
-        <v>-0.036</v>
+        <v>100</v>
       </c>
       <c r="R144" s="22" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S144" s="22" t="n">
-        <v>0</v>
+        <v>52.99</v>
       </c>
       <c r="T144" s="22" t="n">
-        <v>-0.03</v>
+        <v>500</v>
       </c>
       <c r="U144" s="22" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="V144" s="22" t="n">
-        <v>-0.058</v>
+        <v>300</v>
       </c>
       <c r="W144" s="22" t="n">
+        <v>300</v>
+      </c>
+      <c r="X144" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="20" t="inlineStr">
         <is>
-          <t>배당금 지급</t>
-        </is>
-      </c>
-      <c r="D145" s="22" t="n">
-        <v>-69.842</v>
-      </c>
-      <c r="F145" s="22" t="n">
-        <v>-139.688</v>
-      </c>
-      <c r="H145" s="22" t="n">
-        <v>-69.869</v>
-      </c>
-      <c r="J145" s="22" t="n">
-        <v>-139.688</v>
-      </c>
-      <c r="L145" s="22" t="n">
-        <v>-65.682</v>
-      </c>
-      <c r="N145" s="22" t="n">
-        <v>-131.377</v>
+          <t>자회사 주식 취득</t>
+        </is>
       </c>
       <c r="O145" s="22" t="n">
-        <v>-109.64</v>
+        <v>-28.933</v>
       </c>
       <c r="P145" s="22" t="n">
-        <v>-119.772</v>
-      </c>
-      <c r="Q145" s="22" t="n">
-        <v>-129.714</v>
-      </c>
-      <c r="R145" s="22" t="n">
-        <v>-139.623</v>
-      </c>
-      <c r="S145" s="22" t="n">
-        <v>-135.651</v>
-      </c>
-      <c r="T145" s="22" t="n">
-        <v>-131.743</v>
-      </c>
-      <c r="U145" s="22" t="n">
-        <v>-131.568</v>
-      </c>
-      <c r="V145" s="22" t="n">
-        <v>-139.688</v>
-      </c>
-      <c r="W145" s="22" t="n">
-        <v>-139.688</v>
-      </c>
-      <c r="X145" s="22" t="n">
-        <v>-131.377</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="D146" s="12" t="n">
-        <v>-69.842</v>
-      </c>
-      <c r="F146" s="12" t="n">
-        <v>-139.746</v>
-      </c>
-      <c r="H146" s="12" t="n">
-        <v>-69.869</v>
-      </c>
-      <c r="J146" s="12" t="n">
-        <v>-139.688</v>
-      </c>
-      <c r="L146" s="12" t="n">
-        <v>-65.682</v>
-      </c>
-      <c r="N146" s="12" t="n">
-        <v>-131.377</v>
-      </c>
-      <c r="O146" s="12" t="n">
-        <v>-109.64</v>
-      </c>
-      <c r="P146" s="12" t="n">
-        <v>-119.815</v>
-      </c>
-      <c r="Q146" s="12" t="n">
-        <v>-129.751</v>
-      </c>
-      <c r="R146" s="12" t="n">
-        <v>-139.623</v>
-      </c>
-      <c r="S146" s="12" t="n">
-        <v>-135.651</v>
-      </c>
-      <c r="T146" s="12" t="n">
-        <v>-131.774</v>
-      </c>
-      <c r="U146" s="12" t="n">
-        <v>-131.568</v>
-      </c>
-      <c r="V146" s="12" t="n">
-        <v>-139.746</v>
-      </c>
-      <c r="W146" s="12" t="n">
-        <v>-139.688</v>
-      </c>
-      <c r="X146" s="12" t="n">
-        <v>-131.377</v>
+      <c r="A146" s="20" t="inlineStr">
+        <is>
+          <t>대여</t>
+        </is>
+      </c>
+      <c r="D146" s="22" t="n">
+        <v>-20.256</v>
+      </c>
+      <c r="F146" s="22" t="n">
+        <v>-33.219</v>
+      </c>
+      <c r="H146" s="22" t="n">
+        <v>-19.993</v>
+      </c>
+      <c r="J146" s="22" t="n">
+        <v>-40.468</v>
+      </c>
+      <c r="L146" s="22" t="n">
+        <v>-15.165</v>
+      </c>
+      <c r="N146" s="22" t="n">
+        <v>-38.211</v>
+      </c>
+      <c r="P146" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q146" s="22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R146" s="22" t="n">
+        <v>-19.215</v>
+      </c>
+      <c r="S146" s="22" t="n">
+        <v>-26.107</v>
+      </c>
+      <c r="T146" s="22" t="n">
+        <v>-26.803</v>
+      </c>
+      <c r="U146" s="22" t="n">
+        <v>-31.124</v>
+      </c>
+      <c r="V146" s="22" t="n">
+        <v>-33.219</v>
+      </c>
+      <c r="W146" s="22" t="n">
+        <v>-40.468</v>
+      </c>
+      <c r="X146" s="22" t="n">
+        <v>-38.211</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="20" t="inlineStr">
         <is>
-          <t>현금성자산 환산차이</t>
+          <t>대여금 회수</t>
         </is>
       </c>
       <c r="D147" s="22" t="n">
-        <v>-2.258</v>
+        <v>21.152</v>
       </c>
       <c r="F147" s="22" t="n">
-        <v>-0.298</v>
+        <v>34.86</v>
       </c>
       <c r="H147" s="22" t="n">
-        <v>-0.528</v>
+        <v>20.274</v>
       </c>
       <c r="J147" s="22" t="n">
-        <v>-1.094</v>
+        <v>36.405</v>
       </c>
       <c r="L147" s="22" t="n">
-        <v>0.533</v>
+        <v>17.941</v>
       </c>
       <c r="N147" s="22" t="n">
-        <v>0.772</v>
+        <v>40.862</v>
       </c>
       <c r="O147" s="22" t="n">
-        <v>0.004</v>
+        <v>0.856</v>
       </c>
       <c r="P147" s="22" t="n">
-        <v>0</v>
+        <v>0.777</v>
       </c>
       <c r="Q147" s="22" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="R147" s="22" t="n">
-        <v>-0.07199999999999999</v>
+        <v>4.565</v>
       </c>
       <c r="S147" s="22" t="n">
-        <v>1.231</v>
+        <v>19.766</v>
       </c>
       <c r="T147" s="22" t="n">
-        <v>-0.124</v>
+        <v>24.212</v>
       </c>
       <c r="U147" s="22" t="n">
-        <v>0.437</v>
+        <v>34.774</v>
       </c>
       <c r="V147" s="22" t="n">
-        <v>-0.298</v>
+        <v>34.86</v>
       </c>
       <c r="W147" s="22" t="n">
-        <v>-1.094</v>
+        <v>36.405</v>
       </c>
       <c r="X147" s="22" t="n">
-        <v>0.772</v>
+        <v>40.862</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="20" t="inlineStr">
         <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="D148" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" s="22" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="H148" s="22" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="J148" s="22" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="L148" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" s="22" t="n">
+        <v>-0.051</v>
+      </c>
+      <c r="P148" s="22" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="Q148" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R148" s="22" t="n">
+        <v>5.231</v>
+      </c>
+      <c r="S148" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U148" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V148" s="22" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="W148" s="22" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="X148" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="D149" s="12" t="n">
+        <v>-75.584</v>
+      </c>
+      <c r="F149" s="12" t="n">
+        <v>-289.782</v>
+      </c>
+      <c r="H149" s="12" t="n">
+        <v>-1381.36</v>
+      </c>
+      <c r="J149" s="12" t="n">
+        <v>-1894.881</v>
+      </c>
+      <c r="L149" s="12" t="n">
+        <v>-608.626</v>
+      </c>
+      <c r="N149" s="12" t="n">
+        <v>-1067.863</v>
+      </c>
+      <c r="O149" s="12" t="n">
+        <v>-451.604</v>
+      </c>
+      <c r="P149" s="12" t="n">
+        <v>-542.591</v>
+      </c>
+      <c r="Q149" s="12" t="n">
+        <v>-490.396</v>
+      </c>
+      <c r="R149" s="12" t="n">
+        <v>-689.426</v>
+      </c>
+      <c r="S149" s="12" t="n">
+        <v>-306.003</v>
+      </c>
+      <c r="T149" s="12" t="n">
+        <v>-151.467</v>
+      </c>
+      <c r="U149" s="12" t="n">
+        <v>-215.052</v>
+      </c>
+      <c r="V149" s="12" t="n">
+        <v>-289.782</v>
+      </c>
+      <c r="W149" s="12" t="n">
+        <v>-1894.881</v>
+      </c>
+      <c r="X149" s="12" t="n">
+        <v>-1067.863</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="F150" s="22" t="n">
+        <v>-0.058</v>
+      </c>
+      <c r="J150" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" s="22" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="Q150" s="22" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="R150" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T150" s="22" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="U150" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V150" s="22" t="n">
+        <v>-0.058</v>
+      </c>
+      <c r="W150" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="20" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="D151" s="22" t="n">
+        <v>-69.842</v>
+      </c>
+      <c r="F151" s="22" t="n">
+        <v>-139.688</v>
+      </c>
+      <c r="H151" s="22" t="n">
+        <v>-69.869</v>
+      </c>
+      <c r="J151" s="22" t="n">
+        <v>-139.688</v>
+      </c>
+      <c r="L151" s="22" t="n">
+        <v>-65.682</v>
+      </c>
+      <c r="N151" s="22" t="n">
+        <v>-131.377</v>
+      </c>
+      <c r="O151" s="22" t="n">
+        <v>-109.64</v>
+      </c>
+      <c r="P151" s="22" t="n">
+        <v>-119.772</v>
+      </c>
+      <c r="Q151" s="22" t="n">
+        <v>-129.714</v>
+      </c>
+      <c r="R151" s="22" t="n">
+        <v>-139.623</v>
+      </c>
+      <c r="S151" s="22" t="n">
+        <v>-135.651</v>
+      </c>
+      <c r="T151" s="22" t="n">
+        <v>-131.743</v>
+      </c>
+      <c r="U151" s="22" t="n">
+        <v>-131.568</v>
+      </c>
+      <c r="V151" s="22" t="n">
+        <v>-139.688</v>
+      </c>
+      <c r="W151" s="22" t="n">
+        <v>-139.688</v>
+      </c>
+      <c r="X151" s="22" t="n">
+        <v>-131.377</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="D152" s="12" t="n">
+        <v>-69.842</v>
+      </c>
+      <c r="F152" s="12" t="n">
+        <v>-139.746</v>
+      </c>
+      <c r="H152" s="12" t="n">
+        <v>-69.869</v>
+      </c>
+      <c r="J152" s="12" t="n">
+        <v>-139.688</v>
+      </c>
+      <c r="L152" s="12" t="n">
+        <v>-65.682</v>
+      </c>
+      <c r="N152" s="12" t="n">
+        <v>-131.377</v>
+      </c>
+      <c r="O152" s="12" t="n">
+        <v>-109.64</v>
+      </c>
+      <c r="P152" s="12" t="n">
+        <v>-119.815</v>
+      </c>
+      <c r="Q152" s="12" t="n">
+        <v>-129.751</v>
+      </c>
+      <c r="R152" s="12" t="n">
+        <v>-139.623</v>
+      </c>
+      <c r="S152" s="12" t="n">
+        <v>-135.651</v>
+      </c>
+      <c r="T152" s="12" t="n">
+        <v>-131.774</v>
+      </c>
+      <c r="U152" s="12" t="n">
+        <v>-131.568</v>
+      </c>
+      <c r="V152" s="12" t="n">
+        <v>-139.746</v>
+      </c>
+      <c r="W152" s="12" t="n">
+        <v>-139.688</v>
+      </c>
+      <c r="X152" s="12" t="n">
+        <v>-131.377</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="20" t="inlineStr">
+        <is>
+          <t>현금성자산 환산차이</t>
+        </is>
+      </c>
+      <c r="D153" s="22" t="n">
+        <v>-2.258</v>
+      </c>
+      <c r="F153" s="22" t="n">
+        <v>-0.298</v>
+      </c>
+      <c r="H153" s="22" t="n">
+        <v>-0.528</v>
+      </c>
+      <c r="J153" s="22" t="n">
+        <v>-1.094</v>
+      </c>
+      <c r="L153" s="22" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N153" s="22" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="O153" s="22" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="P153" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" s="22" t="n">
+        <v>-0.06900000000000001</v>
+      </c>
+      <c r="R153" s="22" t="n">
+        <v>-0.07199999999999999</v>
+      </c>
+      <c r="S153" s="22" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="T153" s="22" t="n">
+        <v>-0.124</v>
+      </c>
+      <c r="U153" s="22" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="V153" s="22" t="n">
+        <v>-0.298</v>
+      </c>
+      <c r="W153" s="22" t="n">
+        <v>-1.094</v>
+      </c>
+      <c r="X153" s="22" t="n">
+        <v>0.772</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="20" t="inlineStr">
+        <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="D148" s="22" t="n">
+      <c r="D154" s="22" t="n">
         <v>143.068</v>
       </c>
-      <c r="F148" s="22" t="n">
+      <c r="F154" s="22" t="n">
         <v>110.646</v>
       </c>
-      <c r="H148" s="22" t="n">
+      <c r="H154" s="22" t="n">
         <v>-2432.888</v>
       </c>
-      <c r="J148" s="22" t="n">
+      <c r="J154" s="22" t="n">
         <v>-3190.219</v>
       </c>
-      <c r="L148" s="22" t="n">
+      <c r="L154" s="22" t="n">
         <v>-498.035</v>
       </c>
-      <c r="N148" s="22" t="n">
+      <c r="N154" s="22" t="n">
         <v>-255.231</v>
       </c>
-      <c r="O148" s="22" t="n">
+      <c r="O154" s="22" t="n">
         <v>1700.293</v>
       </c>
-      <c r="P148" s="22" t="n">
+      <c r="P154" s="22" t="n">
         <v>15.182</v>
       </c>
-      <c r="Q148" s="22" t="n">
+      <c r="Q154" s="22" t="n">
         <v>307.588</v>
       </c>
-      <c r="R148" s="22" t="n">
+      <c r="R154" s="22" t="n">
         <v>-202.138</v>
       </c>
-      <c r="S148" s="22" t="n">
+      <c r="S154" s="22" t="n">
         <v>372.032</v>
       </c>
-      <c r="T148" s="22" t="n">
+      <c r="T154" s="22" t="n">
         <v>262.208</v>
       </c>
-      <c r="U148" s="22" t="n">
+      <c r="U154" s="22" t="n">
         <v>-85.956</v>
       </c>
-      <c r="V148" s="22" t="n">
+      <c r="V154" s="22" t="n">
         <v>110.646</v>
       </c>
-      <c r="W148" s="22" t="n">
+      <c r="W154" s="22" t="n">
         <v>-3190.219</v>
       </c>
-      <c r="X148" s="22" t="n">
+      <c r="X154" s="22" t="n">
         <v>-255.231</v>
       </c>
     </row>
@@ -9314,7 +9721,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -10724,7 +11131,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -10776,7 +11183,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -10828,7 +11235,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -10880,7 +11287,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -10932,7 +11339,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -10984,7 +11391,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -11036,7 +11443,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -11046,43 +11453,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",H28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",I28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",J28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",K28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",L28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -11106,7 +11513,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -11158,7 +11565,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -11210,7 +11617,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -11262,7 +11669,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -11314,7 +11721,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -11366,7 +11773,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -11436,7 +11843,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -11488,7 +11895,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -11498,49 +11905,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -11550,49 +11957,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -11602,49 +12009,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -11654,43 +12061,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -11714,7 +12121,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -11766,7 +12173,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -11818,7 +12225,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -11870,7 +12277,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -14671,24 +15078,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
